--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55974A76-ACCE-4EEE-8FAE-8F68F7567405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C208883-69A2-4C97-8CB4-4A540A7A8C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">Source: </t>
   </si>
@@ -137,9 +137,6 @@
     <t>Supply Curve Parameters</t>
   </si>
   <si>
-    <t>CSC Capacity Supply Curve Share of Cost Effective Hybrid Capacity Built in a Single Year</t>
-  </si>
-  <si>
     <t>% of total installed capacity</t>
   </si>
   <si>
@@ -162,6 +159,18 @@
   </si>
   <si>
     <t>Incremental Revenue</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>For the Share of Cost Effective Capacity Built in a Single Year, we use a value of 1 for all resources except wind,</t>
+  </si>
+  <si>
+    <t>which in recent years has faced unique siting constraints that have limited new capacity.</t>
+  </si>
+  <si>
+    <t>For onshore wind, we use a value of 0.75.</t>
   </si>
 </sst>
 </file>
@@ -205,9 +214,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -292,624 +302,624 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>About!$C$21:$C$121</c:f>
+              <c:f>About!$C$24:$C$124</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>0.25</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75</c:v>
+                  <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.25</c:v>
+                  <c:v>2500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.75</c:v>
+                  <c:v>3500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.25</c:v>
+                  <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.75</c:v>
+                  <c:v>5500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.25</c:v>
+                  <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.5</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.75</c:v>
+                  <c:v>7500</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.25</c:v>
+                  <c:v>8500</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.5</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.75</c:v>
+                  <c:v>9500</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.25</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.5</c:v>
+                  <c:v>11000</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.75</c:v>
+                  <c:v>11500</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.25</c:v>
+                  <c:v>12500</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.5</c:v>
+                  <c:v>13000</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.75</c:v>
+                  <c:v>13500</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>7</c:v>
+                  <c:v>14000</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7.25</c:v>
+                  <c:v>14500</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7.5</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.75</c:v>
+                  <c:v>15500</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>8</c:v>
+                  <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8.25</c:v>
+                  <c:v>16500</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.5</c:v>
+                  <c:v>17000</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>8.75</c:v>
+                  <c:v>17500</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>9</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>9.25</c:v>
+                  <c:v>18500</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>9.5</c:v>
+                  <c:v>19000</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>9.75</c:v>
+                  <c:v>19500</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>10</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10.25</c:v>
+                  <c:v>20500</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>10.5</c:v>
+                  <c:v>21000</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>10.75</c:v>
+                  <c:v>21500</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>11</c:v>
+                  <c:v>22000</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>11.25</c:v>
+                  <c:v>22500</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>11.5</c:v>
+                  <c:v>23000</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>11.75</c:v>
+                  <c:v>23500</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>12</c:v>
+                  <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>12.25</c:v>
+                  <c:v>24500</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>12.5</c:v>
+                  <c:v>25000</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>12.75</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>13</c:v>
+                  <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>13.25</c:v>
+                  <c:v>26500</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>13.5</c:v>
+                  <c:v>27000</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>13.75</c:v>
+                  <c:v>27500</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>14</c:v>
+                  <c:v>28000</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>14.25</c:v>
+                  <c:v>28500</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>14.5</c:v>
+                  <c:v>29000</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>14.75</c:v>
+                  <c:v>29500</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>15</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>15.25</c:v>
+                  <c:v>30500</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>15.5</c:v>
+                  <c:v>31000</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>15.75</c:v>
+                  <c:v>31500</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>16</c:v>
+                  <c:v>32000</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>16.25</c:v>
+                  <c:v>32500</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>16.5</c:v>
+                  <c:v>33000</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>16.75</c:v>
+                  <c:v>33500</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>17</c:v>
+                  <c:v>34000</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>17.25</c:v>
+                  <c:v>34500</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>17.5</c:v>
+                  <c:v>35000</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>17.75</c:v>
+                  <c:v>35500</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>18</c:v>
+                  <c:v>36000</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>18.25</c:v>
+                  <c:v>36500</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>18.5</c:v>
+                  <c:v>37000</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>18.75</c:v>
+                  <c:v>37500</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>19</c:v>
+                  <c:v>38000</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>19.25</c:v>
+                  <c:v>38500</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>19.5</c:v>
+                  <c:v>39000</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>19.75</c:v>
+                  <c:v>39500</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>20</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>20.25</c:v>
+                  <c:v>40500</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>20.5</c:v>
+                  <c:v>41000</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>20.75</c:v>
+                  <c:v>41500</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>21</c:v>
+                  <c:v>42000</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>21.25</c:v>
+                  <c:v>42500</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>21.5</c:v>
+                  <c:v>43000</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>21.75</c:v>
+                  <c:v>43500</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>22</c:v>
+                  <c:v>44000</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>22.25</c:v>
+                  <c:v>44500</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>22.5</c:v>
+                  <c:v>45000</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>22.75</c:v>
+                  <c:v>45500</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>23</c:v>
+                  <c:v>46000</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>23.25</c:v>
+                  <c:v>46500</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>23.5</c:v>
+                  <c:v>47000</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>23.75</c:v>
+                  <c:v>47500</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>24</c:v>
+                  <c:v>48000</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>24.25</c:v>
+                  <c:v>48500</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>24.5</c:v>
+                  <c:v>49000</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>24.75</c:v>
+                  <c:v>49500</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>25</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>25.25</c:v>
+                  <c:v>50500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>About!$B$21:$B$121</c:f>
+              <c:f>About!$B$24:$B$124</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>2.9387164590499728E-6</c:v>
+                  <c:v>3.3489752805648809E-7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.3508987656584158E-5</c:v>
+                  <c:v>2.6791551015481474E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.9336018158404631E-5</c:v>
+                  <c:v>9.041918329455445E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.8802429327882398E-4</c:v>
+                  <c:v>2.1431633037929942E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.6713369702505162E-4</c:v>
+                  <c:v>4.1855238076579648E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.3414614007045462E-4</c:v>
+                  <c:v>7.2317035876470759E-5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.006422790718059E-3</c:v>
+                  <c:v>1.1481724169225271E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.5011520593627675E-3</c:v>
+                  <c:v>1.7135021303994746E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.1352885583158314E-3</c:v>
+                  <c:v>2.4390236156555944E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.9254833434584626E-3</c:v>
+                  <c:v>3.3444975044409631E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.8880058412656712E-3</c:v>
+                  <c:v>4.4495538141219038E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.0386579732422526E-3</c:v>
+                  <c:v>5.7736617667798751E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.3926811083940913E-3</c:v>
+                  <c:v>7.336096622230226E-4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.9646566013662247E-3</c:v>
+                  <c:v>9.1559036041015396E-4</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.7684008073131972E-3</c:v>
+                  <c:v>1.1251859013301779E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.1816855602081967E-2</c:v>
+                  <c:v>1.3642428639517451E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.4121975575197189E-2</c:v>
+                  <c:v>1.6345723598757272E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.6694613200417676E-2</c:v>
+                  <c:v>1.9379453743239433E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.9544403420951564E-2</c:v>
+                  <c:v>2.2760878809044566E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.267964921017894E-2</c:v>
+                  <c:v>2.6506757486755017E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.6107209780122643E-2</c:v>
+                  <c:v>3.0633294620639323E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.9832393204970647E-2</c:v>
+                  <c:v>3.5156086762653666E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>3.3858855301670994E-2</c:v>
+                  <c:v>4.0090066328439117E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3.8188506660006477E-2</c:v>
+                  <c:v>4.5449444623392177E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4.2821429736777793E-2</c:v>
+                  <c:v>5.1247654027590517E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.7755807919210802E-2</c:v>
+                  <c:v>5.7497289648605621E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>5.2987868418287974E-2</c:v>
+                  <c:v>6.4210050770837218E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.8511840770746393E-2</c:v>
+                  <c:v>7.139668244867739E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>6.4319932607017835E-2</c:v>
+                  <c:v>7.9066917608325293E-3</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7.040232418023408E-2</c:v>
+                  <c:v>8.7229420039149769E-3</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.6747182948336296E-2</c:v>
+                  <c:v>9.5891728669876136E-3</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>8.3340699258080464E-2</c:v>
+                  <c:v>1.0506020353728399E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>9.0167143898212704E-2</c:v>
+                  <c:v>1.1473997386527171E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>9.7208947972360321E-2</c:v>
+                  <c:v>1.2493488867981531E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.10444680519450757</c:v>
+                  <c:v>1.3564747039025687E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.11185979633676199</c:v>
+                  <c:v>1.4687887176925568E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.11942553516706651</c:v>
+                  <c:v>1.5862883676240225E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.12712033481123883</c:v>
+                  <c:v>1.7089566555369529E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.13491939306780171</c:v>
+                  <c:v>1.8367618430465693E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.14279699480482452</c:v>
+                  <c:v>1.9696571997260381E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.15072672918526989</c:v>
+                  <c:v>2.1075808059742129E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.15868171911122922</c:v>
+                  <c:v>2.2504554142594765E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.16663485995800573</c:v>
+                  <c:v>2.3981883721876138E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.17455906439599175</c:v>
+                  <c:v>2.5506716105570884E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.18242750988073522</c:v>
+                  <c:v>2.7077816992397724E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.19021388523755758</c:v>
+                  <c:v>2.8693799733595995E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.19789263268329291</c:v>
+                  <c:v>3.035312731837099E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.20543918161928124</c:v>
+                  <c:v>3.2054115099261718E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.21283017059990736</c:v>
+                  <c:v>3.3794934268928725E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.22004365403087262</c:v>
+                  <c:v>3.5573616094775717E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.22705929037995962</c:v>
+                  <c:v>3.7388056912446274E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.23385850898689628</c:v>
+                  <c:v>3.9236023873619186E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.24042465293238419</c:v>
+                  <c:v>4.1115161437703815E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.2467430958615193</c:v>
+                  <c:v>4.3022998591062303E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.25280133114377951</c:v>
+                  <c:v>4.495695677130844E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.2585890322787715</c:v>
+                  <c:v>4.6914358468115175E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.26409808401086282</c:v>
+                  <c:v>4.8892436465861083E-2</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.26932258418246974</c:v>
+                  <c:v>5.0888343687428006E-2</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.27425881692032672</c:v>
+                  <c:v>5.2899163592589921E-2</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.2789051982966137</c:v>
+                  <c:v>5.4921921078778663E-2</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.28326219612285092</c:v>
+                  <c:v>5.6953593826638713E-2</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.2873322260053523</c:v>
+                  <c:v>5.8991124027762909E-2</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.29111952620450759</c:v>
+                  <c:v>6.1031430427395852E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.29463001418577178</c:v>
+                  <c:v>6.3071420610770493E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.29787112801967686</c:v>
+                  <c:v>6.5108003458162492E-2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.30085165597558955</c:v>
+                  <c:v>6.7138101690766061E-2</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.30358155775609158</c:v>
+                  <c:v>6.915866442716484E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.30607178083525383</c:v>
+                  <c:v>7.1166679668536584E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.30833407529690587</c:v>
+                  <c:v>7.3159186629829842E-2</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.31038081042304033</c:v>
+                  <c:v>7.5133287834015461E-2</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.31222479606484704</c:v>
+                  <c:v>7.7086160887166397E-2</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.31387911154870857</c:v>
+                  <c:v>7.9015069853569708E-2</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.31535694453758484</c:v>
+                  <c:v>8.0917376152326803E-2</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.31667144189658553</c:v>
+                  <c:v>8.2790548899946304E-2</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.3178355742128724</c:v>
+                  <c:v>8.4632174627258694E-2</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.31886201520731511</c:v>
+                  <c:v>8.643996630355924E-2</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.31976303686122226</c:v>
+                  <c:v>8.8211771606171191E-2</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.32055042067798994</c:v>
+                  <c:v>8.9945580379575493E-2</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.32123538511752886</c:v>
+                  <c:v>9.1639531234810279E-2</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.32182852889030422</c:v>
+                  <c:v>9.32919172469414E-2</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.32233978948549169</c:v>
+                  <c:v>9.4901190715968961E-2</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.32277841604000762</c:v>
+                  <c:v>9.6465966964479927E-2</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.32315295543592437</c:v>
+                  <c:v>9.7985027153597692E-2</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.32347125034502283</c:v>
+                  <c:v>9.9457320107219804E-2</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.32374044782105788</c:v>
+                  <c:v>0.10088196314308123</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.32396701697112512</c:v>
+                  <c:v>0.10225824191772932</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.32415677421421263</c:v>
+                  <c:v>0.1035856093009499</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.32431491465326501</c:v>
+                  <c:v>0.10486368330344273</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.32444604814158295</c:v>
+                  <c:v>0.10609224408950788</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.3245542387092018</c:v>
+                  <c:v>0.10727123011408218</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.32464304612372757</c:v>
+                  <c:v>0.10840073343056618</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.32471556848661476</c:v>
+                  <c:v>0.10948099422242338</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.32477448490384953</c:v>
+                  <c:v>0.11051239461744319</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.32482209741368234</c:v>
+                  <c:v>0.11149545184876868</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.32486037149823072</c:v>
+                  <c:v>0.11243081083124459</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.3248909746459317</c:v>
+                  <c:v>0.11331923622529684</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.32491531256425021</c:v>
+                  <c:v>0.11416160406337549</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.32493456276384014</c:v>
+                  <c:v>0.11495889301595999</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.32494970534441392</c:v>
+                  <c:v>0.11571217537522674</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.32496155090760193</c:v>
+                  <c:v>0.11642260783471928</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.32497076560245858</c:v>
+                  <c:v>0.11709142214275396</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1066,6 +1076,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1073,7 +1084,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1195,124 +1205,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
+                  <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.75</c:v>
+                  <c:v>2250</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.25</c:v>
+                  <c:v>3750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5</c:v>
+                  <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.75</c:v>
+                  <c:v>5250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.25</c:v>
+                  <c:v>6750</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.5</c:v>
+                  <c:v>7500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.75</c:v>
+                  <c:v>8250</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.25</c:v>
+                  <c:v>9750</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.5</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.75</c:v>
+                  <c:v>11250</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.25</c:v>
+                  <c:v>12750</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.5</c:v>
+                  <c:v>13500</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.75</c:v>
+                  <c:v>14250</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.25</c:v>
+                  <c:v>15750</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.5</c:v>
+                  <c:v>16500</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.75</c:v>
+                  <c:v>17250</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.25</c:v>
+                  <c:v>18750</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.5</c:v>
+                  <c:v>19500</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6.75</c:v>
+                  <c:v>20250</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7</c:v>
+                  <c:v>21000</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7.25</c:v>
+                  <c:v>21750</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.5</c:v>
+                  <c:v>22500</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7.75</c:v>
+                  <c:v>23250</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8</c:v>
+                  <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.25</c:v>
+                  <c:v>24750</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>8.5</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>8.75</c:v>
+                  <c:v>26250</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>9</c:v>
+                  <c:v>27000</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>9.25</c:v>
+                  <c:v>27750</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>9.5</c:v>
+                  <c:v>28500</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>9.75</c:v>
+                  <c:v>29250</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1327,124 +1337,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.9387164590499728E-6</c:v>
+                  <c:v>1.1302755611730664E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3508987656584158E-5</c:v>
+                  <c:v>9.041918329455445E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.9336018158404631E-5</c:v>
+                  <c:v>3.0513853137847935E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.8802429327882398E-4</c:v>
+                  <c:v>7.2317035876470759E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.6713369702505162E-4</c:v>
+                  <c:v>1.4120526808655831E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.3414614007045462E-4</c:v>
+                  <c:v>2.4390236156555944E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.006422790718059E-3</c:v>
+                  <c:v>3.8708568873771498E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5011520593627675E-3</c:v>
+                  <c:v>5.7736617667798751E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.1352885583158314E-3</c:v>
+                  <c:v>8.2126483012147367E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.9254833434584626E-3</c:v>
+                  <c:v>1.1251859013301779E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.8880058412656712E-3</c:v>
+                  <c:v>1.4953868620252581E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.0386579732422526E-3</c:v>
+                  <c:v>1.9379453743239433E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.3926811083940913E-3</c:v>
+                  <c:v>2.4587235032284965E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.9646566013662247E-3</c:v>
+                  <c:v>3.0633294620639323E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.7684008073131972E-3</c:v>
+                  <c:v>3.7570772335819985E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.1816855602081967E-2</c:v>
+                  <c:v>4.5449444623392177E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.4121975575197189E-2</c:v>
+                  <c:v>5.4315290673835337E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.6694613200417676E-2</c:v>
+                  <c:v>6.4210050770837218E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.9544403420951564E-2</c:v>
+                  <c:v>7.5170782388275237E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.267964921017894E-2</c:v>
+                  <c:v>8.7229420039149769E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.6107209780122643E-2</c:v>
+                  <c:v>1.0041234530816401E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.9832393204970647E-2</c:v>
+                  <c:v>1.1473997386527171E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3.3858855301670994E-2</c:v>
+                  <c:v>1.3022636654488842E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.8188506660006477E-2</c:v>
+                  <c:v>1.4687887176925568E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.2821429736777793E-2</c:v>
+                  <c:v>1.6469780667991457E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.7755807919210802E-2</c:v>
+                  <c:v>1.8367618430465693E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.2987868418287974E-2</c:v>
+                  <c:v>2.0379949391649221E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.8511840770746393E-2</c:v>
+                  <c:v>2.2504554142594765E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.4319932607017835E-2</c:v>
+                  <c:v>2.4738435618083782E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.040232418023408E-2</c:v>
+                  <c:v>2.7077816992397724E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7.6747182948336296E-2</c:v>
+                  <c:v>2.951814728782165E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8.3340699258080464E-2</c:v>
+                  <c:v>3.2054115099261718E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>9.0167143898212704E-2</c:v>
+                  <c:v>3.467967073008181E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>9.7208947972360321E-2</c:v>
+                  <c:v>3.7388056912446274E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.10444680519450757</c:v>
+                  <c:v>4.0171848151733677E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.11185979633676199</c:v>
+                  <c:v>4.3022998591062303E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.11942553516706651</c:v>
+                  <c:v>4.5932898141179429E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.12712033481123883</c:v>
+                  <c:v>4.8892436465861083E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.13491939306780171</c:v>
+                  <c:v>5.1892074256846804E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.14279699480482452</c:v>
+                  <c:v>5.4921921078778663E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1601,6 +1611,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1608,7 +1619,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1730,124 +1740,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
+                  <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.75</c:v>
+                  <c:v>2250</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.25</c:v>
+                  <c:v>3750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5</c:v>
+                  <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.75</c:v>
+                  <c:v>5250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.25</c:v>
+                  <c:v>6750</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.5</c:v>
+                  <c:v>7500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.75</c:v>
+                  <c:v>8250</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.25</c:v>
+                  <c:v>9750</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.5</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.75</c:v>
+                  <c:v>11250</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.25</c:v>
+                  <c:v>12750</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.5</c:v>
+                  <c:v>13500</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.75</c:v>
+                  <c:v>14250</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.25</c:v>
+                  <c:v>15750</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.5</c:v>
+                  <c:v>16500</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.75</c:v>
+                  <c:v>17250</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.25</c:v>
+                  <c:v>18750</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.5</c:v>
+                  <c:v>19500</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6.75</c:v>
+                  <c:v>20250</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7</c:v>
+                  <c:v>21000</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7.25</c:v>
+                  <c:v>21750</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.5</c:v>
+                  <c:v>22500</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7.75</c:v>
+                  <c:v>23250</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8</c:v>
+                  <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.25</c:v>
+                  <c:v>24750</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>8.5</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>8.75</c:v>
+                  <c:v>26250</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>9</c:v>
+                  <c:v>27000</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>9.25</c:v>
+                  <c:v>27750</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>9.5</c:v>
+                  <c:v>28500</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>9.75</c:v>
+                  <c:v>29250</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1862,124 +1872,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.9387164590499728E-6</c:v>
+                  <c:v>1.1302755611730664E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.3508987656584158E-5</c:v>
+                  <c:v>9.041918329455445E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.9336018158404631E-5</c:v>
+                  <c:v>3.0513853137847935E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.8802429327882398E-4</c:v>
+                  <c:v>7.2317035876470759E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.6713369702505162E-4</c:v>
+                  <c:v>1.4120526808655831E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.3414614007045462E-4</c:v>
+                  <c:v>2.4390236156555944E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.006422790718059E-3</c:v>
+                  <c:v>3.8708568873771498E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5011520593627675E-3</c:v>
+                  <c:v>5.7736617667798751E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.1352885583158314E-3</c:v>
+                  <c:v>8.2126483012147367E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.9254833434584626E-3</c:v>
+                  <c:v>1.1251859013301779E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.8880058412656712E-3</c:v>
+                  <c:v>1.4953868620252581E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.0386579732422526E-3</c:v>
+                  <c:v>1.9379453743239433E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.3926811083940913E-3</c:v>
+                  <c:v>2.4587235032284965E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.9646566013662247E-3</c:v>
+                  <c:v>3.0633294620639323E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.7684008073131972E-3</c:v>
+                  <c:v>3.7570772335819985E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.1816855602081967E-2</c:v>
+                  <c:v>4.5449444623392177E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.4121975575197189E-2</c:v>
+                  <c:v>5.4315290673835337E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.6694613200417676E-2</c:v>
+                  <c:v>6.4210050770837218E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.9544403420951564E-2</c:v>
+                  <c:v>7.5170782388275237E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.267964921017894E-2</c:v>
+                  <c:v>8.7229420039149769E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.6107209780122643E-2</c:v>
+                  <c:v>1.0041234530816401E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.9832393204970647E-2</c:v>
+                  <c:v>1.1473997386527171E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3.3858855301670994E-2</c:v>
+                  <c:v>1.3022636654488842E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>3.8188506660006477E-2</c:v>
+                  <c:v>1.4687887176925568E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4.2821429736777793E-2</c:v>
+                  <c:v>1.6469780667991457E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4.7755807919210802E-2</c:v>
+                  <c:v>1.8367618430465693E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>5.2987868418287974E-2</c:v>
+                  <c:v>2.0379949391649221E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>5.8511840770746393E-2</c:v>
+                  <c:v>2.2504554142594765E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>6.4319932607017835E-2</c:v>
+                  <c:v>2.4738435618083782E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.040232418023408E-2</c:v>
+                  <c:v>2.7077816992397724E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7.6747182948336296E-2</c:v>
+                  <c:v>2.951814728782165E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8.3340699258080464E-2</c:v>
+                  <c:v>3.2054115099261718E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>9.0167143898212704E-2</c:v>
+                  <c:v>3.467967073008181E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>9.7208947972360321E-2</c:v>
+                  <c:v>3.7388056912446274E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.10444680519450757</c:v>
+                  <c:v>4.0171848151733677E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.11185979633676199</c:v>
+                  <c:v>4.3022998591062303E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.11942553516706651</c:v>
+                  <c:v>4.5932898141179429E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.12712033481123883</c:v>
+                  <c:v>4.8892436465861083E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.13491939306780171</c:v>
+                  <c:v>5.1892074256846804E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.14279699480482452</c:v>
+                  <c:v>5.4921921078778663E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2136,6 +2146,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2143,7 +2154,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3850,16 +3860,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>151130</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>5019675</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>132080</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>138430</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3888,13 +3898,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>5210175</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -4263,1108 +4273,1124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3D2DEE-686E-48A0-AC3D-0F54DEA5D0EC}">
-  <dimension ref="A1:C121"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C124"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="88.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="88.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>38</v>
       </c>
-      <c r="B12">
-        <v>0.32500000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="B18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>39</v>
       </c>
-      <c r="B15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20">
-        <f>(1-EXP(-((C20/$B$16-($B$15-0.5))/$B$13)^$B$14))*$B$12</f>
+      <c r="B19">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B23">
+        <f>(1-EXP(-((C23/$B$19-($B$18-0.5))/$B$16)^$B$17))*$B$15</f>
         <v>0</v>
       </c>
-      <c r="C20">
+      <c r="C23">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21">
-        <f t="shared" ref="B21:B84" si="0">(1-EXP(-((C21/$B$16-($B$15-0.5))/$B$13)^$B$14))*$B$12</f>
-        <v>2.9387164590499728E-6</v>
-      </c>
-      <c r="C21">
-        <f>C20+0.25</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <f t="shared" si="0"/>
-        <v>2.3508987656584158E-5</v>
-      </c>
-      <c r="C22">
-        <f t="shared" ref="C22:C85" si="1">C21+0.25</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23">
-        <f t="shared" si="0"/>
-        <v>7.9336018158404631E-5</v>
-      </c>
-      <c r="C23">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24">
-        <f t="shared" si="0"/>
-        <v>1.8802429327882398E-4</v>
+        <f t="shared" ref="B24:B87" si="0">(1-EXP(-((C24/$B$19-($B$18-0.5))/$B$16)^$B$17))*$B$15</f>
+        <v>3.3489752805648809E-7</v>
       </c>
       <c r="C24">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B25">
         <f t="shared" si="0"/>
-        <v>3.6713369702505162E-4</v>
+        <v>2.6791551015481474E-6</v>
       </c>
       <c r="C25">
-        <f t="shared" si="1"/>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26">
         <f t="shared" si="0"/>
-        <v>6.3414614007045462E-4</v>
+        <v>9.041918329455445E-6</v>
       </c>
       <c r="C26">
-        <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+        <f>C25+500</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27">
         <f t="shared" si="0"/>
-        <v>1.006422790718059E-3</v>
+        <v>2.1431633037929942E-5</v>
       </c>
       <c r="C27">
-        <f t="shared" si="1"/>
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" ref="C27:C90" si="1">C26+500</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>1.5011520593627675E-3</v>
+        <v>4.1855238076579648E-5</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29">
         <f t="shared" si="0"/>
-        <v>2.1352885583158314E-3</v>
+        <v>7.2317035876470759E-5</v>
       </c>
       <c r="C29">
         <f t="shared" si="1"/>
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B30">
         <f t="shared" si="0"/>
-        <v>2.9254833434584626E-3</v>
+        <v>1.1481724169225271E-4</v>
       </c>
       <c r="C30">
         <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>3.8880058412656712E-3</v>
+        <v>1.7135021303994746E-4</v>
       </c>
       <c r="C31">
         <f t="shared" si="1"/>
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32">
         <f t="shared" si="0"/>
-        <v>5.0386579732422526E-3</v>
+        <v>2.4390236156555944E-4</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>6.3926811083940913E-3</v>
+        <v>3.3444975044409631E-4</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>7.9646566013662247E-3</v>
+        <v>4.4495538141219038E-4</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35">
         <f t="shared" si="0"/>
-        <v>9.7684008073131972E-3</v>
+        <v>5.7736617667798751E-4</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>1.1816855602081967E-2</v>
+        <v>7.336096622230226E-4</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37">
         <f t="shared" si="0"/>
-        <v>1.4121975575197189E-2</v>
+        <v>9.1559036041015396E-4</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38">
         <f t="shared" si="0"/>
-        <v>1.6694613200417676E-2</v>
+        <v>1.1251859013301779E-3</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39">
         <f t="shared" si="0"/>
-        <v>1.9544403420951564E-2</v>
+        <v>1.3642428639517451E-3</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40">
         <f t="shared" si="0"/>
-        <v>2.267964921017894E-2</v>
+        <v>1.6345723598757272E-3</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>2.6107209780122643E-2</v>
+        <v>1.9379453743239433E-3</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B42">
         <f t="shared" si="0"/>
-        <v>2.9832393204970647E-2</v>
+        <v>2.2760878809044566E-3</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B43">
         <f t="shared" si="0"/>
-        <v>3.3858855301670994E-2</v>
+        <v>2.6506757486755017E-3</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B44">
         <f t="shared" si="0"/>
-        <v>3.8188506660006477E-2</v>
+        <v>3.0633294620639323E-3</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>4.2821429736777793E-2</v>
+        <v>3.5156086762653666E-3</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B46">
         <f t="shared" si="0"/>
-        <v>4.7755807919210802E-2</v>
+        <v>4.0090066328439117E-3</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B47">
         <f t="shared" si="0"/>
-        <v>5.2987868418287974E-2</v>
+        <v>4.5449444623392177E-3</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B48">
         <f t="shared" si="0"/>
-        <v>5.8511840770746393E-2</v>
+        <v>5.1247654027590517E-3</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B49">
         <f t="shared" si="0"/>
-        <v>6.4319932607017835E-2</v>
+        <v>5.7497289648605621E-3</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B50">
         <f t="shared" si="0"/>
-        <v>7.040232418023408E-2</v>
+        <v>6.4210050770837218E-3</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>7.6747182948336296E-2</v>
+        <v>7.139668244867739E-3</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B52">
         <f t="shared" si="0"/>
-        <v>8.3340699258080464E-2</v>
+        <v>7.9066917608325293E-3</v>
       </c>
       <c r="C52">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B53">
         <f t="shared" si="0"/>
-        <v>9.0167143898212704E-2</v>
+        <v>8.7229420039149769E-3</v>
       </c>
       <c r="C53">
         <f t="shared" si="1"/>
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>9.7208947972360321E-2</v>
+        <v>9.5891728669876136E-3</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B55">
         <f t="shared" si="0"/>
-        <v>0.10444680519450757</v>
+        <v>1.0506020353728399E-2</v>
       </c>
       <c r="C55">
         <f t="shared" si="1"/>
-        <v>8.75</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>0.11185979633676199</v>
+        <v>1.1473997386527171E-2</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B57">
         <f t="shared" si="0"/>
-        <v>0.11942553516706651</v>
+        <v>1.2493488867981531E-2</v>
       </c>
       <c r="C57">
         <f t="shared" si="1"/>
-        <v>9.25</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B58">
         <f t="shared" si="0"/>
-        <v>0.12712033481123883</v>
+        <v>1.3564747039025687E-2</v>
       </c>
       <c r="C58">
         <f t="shared" si="1"/>
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B59">
         <f t="shared" si="0"/>
-        <v>0.13491939306780171</v>
+        <v>1.4687887176925568E-2</v>
       </c>
       <c r="C59">
         <f t="shared" si="1"/>
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B60">
         <f t="shared" si="0"/>
-        <v>0.14279699480482452</v>
+        <v>1.5862883676240225E-2</v>
       </c>
       <c r="C60">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B61">
         <f t="shared" si="0"/>
-        <v>0.15072672918526989</v>
+        <v>1.7089566555369529E-2</v>
       </c>
       <c r="C61">
         <f t="shared" si="1"/>
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B62">
         <f t="shared" si="0"/>
-        <v>0.15868171911122922</v>
+        <v>1.8367618430465693E-2</v>
       </c>
       <c r="C62">
         <f t="shared" si="1"/>
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B63">
         <f t="shared" si="0"/>
-        <v>0.16663485995800573</v>
+        <v>1.9696571997260381E-2</v>
       </c>
       <c r="C63">
         <f t="shared" si="1"/>
-        <v>10.75</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>0.17455906439599175</v>
+        <v>2.1075808059742129E-2</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+        <v>20500</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>0.18242750988073522</v>
+        <v>2.2504554142594765E-2</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
-        <v>11.25</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B66">
         <f t="shared" si="0"/>
-        <v>0.19021388523755758</v>
+        <v>2.3981883721876138E-2</v>
       </c>
       <c r="C66">
         <f t="shared" si="1"/>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>0.19789263268329291</v>
+        <v>2.5506716105570884E-2</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
-        <v>11.75</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B68">
         <f t="shared" si="0"/>
-        <v>0.20543918161928124</v>
+        <v>2.7077816992397724E-2</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B69">
         <f t="shared" si="0"/>
-        <v>0.21283017059990736</v>
+        <v>2.8693799733595995E-2</v>
       </c>
       <c r="C69">
         <f t="shared" si="1"/>
-        <v>12.25</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B70">
         <f t="shared" si="0"/>
-        <v>0.22004365403087262</v>
+        <v>3.035312731837099E-2</v>
       </c>
       <c r="C70">
         <f t="shared" si="1"/>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B71">
         <f t="shared" si="0"/>
-        <v>0.22705929037995962</v>
+        <v>3.2054115099261718E-2</v>
       </c>
       <c r="C71">
         <f t="shared" si="1"/>
-        <v>12.75</v>
-      </c>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B72">
         <f t="shared" si="0"/>
-        <v>0.23385850898689628</v>
+        <v>3.3794934268928725E-2</v>
       </c>
       <c r="C72">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B73">
         <f t="shared" si="0"/>
-        <v>0.24042465293238419</v>
+        <v>3.5573616094775717E-2</v>
       </c>
       <c r="C73">
         <f t="shared" si="1"/>
-        <v>13.25</v>
-      </c>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B74">
         <f t="shared" si="0"/>
-        <v>0.2467430958615193</v>
+        <v>3.7388056912446274E-2</v>
       </c>
       <c r="C74">
         <f t="shared" si="1"/>
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B75">
         <f t="shared" si="0"/>
-        <v>0.25280133114377951</v>
+        <v>3.9236023873619186E-2</v>
       </c>
       <c r="C75">
         <f t="shared" si="1"/>
-        <v>13.75</v>
-      </c>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B76">
         <f t="shared" si="0"/>
-        <v>0.2585890322787715</v>
+        <v>4.1115161437703815E-2</v>
       </c>
       <c r="C76">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+        <v>26500</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B77">
         <f t="shared" si="0"/>
-        <v>0.26409808401086282</v>
+        <v>4.3022998591062303E-2</v>
       </c>
       <c r="C77">
         <f t="shared" si="1"/>
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B78">
         <f t="shared" si="0"/>
-        <v>0.26932258418246974</v>
+        <v>4.495695677130844E-2</v>
       </c>
       <c r="C78">
         <f t="shared" si="1"/>
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B79">
         <f t="shared" si="0"/>
-        <v>0.27425881692032672</v>
+        <v>4.6914358468115175E-2</v>
       </c>
       <c r="C79">
         <f t="shared" si="1"/>
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B80">
         <f t="shared" si="0"/>
-        <v>0.2789051982966137</v>
+        <v>4.8892436465861083E-2</v>
       </c>
       <c r="C80">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+        <v>28500</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B81">
         <f t="shared" si="0"/>
-        <v>0.28326219612285092</v>
+        <v>5.0888343687428006E-2</v>
       </c>
       <c r="C81">
         <f t="shared" si="1"/>
-        <v>15.25</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B82">
         <f t="shared" si="0"/>
-        <v>0.2873322260053523</v>
+        <v>5.2899163592589921E-2</v>
       </c>
       <c r="C82">
         <f t="shared" si="1"/>
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+        <v>29500</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B83">
         <f t="shared" si="0"/>
-        <v>0.29111952620450759</v>
+        <v>5.4921921078778663E-2</v>
       </c>
       <c r="C83">
         <f t="shared" si="1"/>
-        <v>15.75</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B84">
         <f t="shared" si="0"/>
-        <v>0.29463001418577178</v>
+        <v>5.6953593826638713E-2</v>
       </c>
       <c r="C84">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+        <v>30500</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B85">
-        <f t="shared" ref="B85:B121" si="2">(1-EXP(-((C85/$B$16-($B$15-0.5))/$B$13)^$B$14))*$B$12</f>
-        <v>0.29787112801967686</v>
+        <f t="shared" si="0"/>
+        <v>5.8991124027762909E-2</v>
       </c>
       <c r="C85">
         <f t="shared" si="1"/>
-        <v>16.25</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B86">
-        <f t="shared" si="2"/>
-        <v>0.30085165597558955</v>
+        <f t="shared" si="0"/>
+        <v>6.1031430427395852E-2</v>
       </c>
       <c r="C86">
-        <f t="shared" ref="C86:C121" si="3">C85+0.25</f>
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>31500</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B87">
-        <f t="shared" si="2"/>
-        <v>0.30358155775609158</v>
+        <f t="shared" si="0"/>
+        <v>6.3071420610770493E-2</v>
       </c>
       <c r="C87">
-        <f t="shared" si="3"/>
-        <v>16.75</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B88">
-        <f t="shared" si="2"/>
-        <v>0.30607178083525383</v>
+        <f t="shared" ref="B88:B124" si="2">(1-EXP(-((C88/$B$19-($B$18-0.5))/$B$16)^$B$17))*$B$15</f>
+        <v>6.5108003458162492E-2</v>
       </c>
       <c r="C88">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B89">
         <f t="shared" si="2"/>
-        <v>0.30833407529690587</v>
+        <v>6.7138101690766061E-2</v>
       </c>
       <c r="C89">
-        <f t="shared" si="3"/>
-        <v>17.25</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B90">
         <f t="shared" si="2"/>
-        <v>0.31038081042304033</v>
+        <v>6.915866442716484E-2</v>
       </c>
       <c r="C90">
-        <f t="shared" si="3"/>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>33500</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B91">
         <f t="shared" si="2"/>
-        <v>0.31222479606484704</v>
+        <v>7.1166679668536584E-2</v>
       </c>
       <c r="C91">
-        <f t="shared" si="3"/>
-        <v>17.75</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" ref="C91:C124" si="3">C90+500</f>
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B92">
         <f t="shared" si="2"/>
-        <v>0.31387911154870857</v>
+        <v>7.3159186629829842E-2</v>
       </c>
       <c r="C92">
         <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+        <v>34500</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B93">
         <f t="shared" si="2"/>
-        <v>0.31535694453758484</v>
+        <v>7.5133287834015461E-2</v>
       </c>
       <c r="C93">
         <f t="shared" si="3"/>
-        <v>18.25</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B94">
         <f t="shared" si="2"/>
-        <v>0.31667144189658553</v>
+        <v>7.7086160887166397E-2</v>
       </c>
       <c r="C94">
         <f t="shared" si="3"/>
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+        <v>35500</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B95">
         <f t="shared" si="2"/>
-        <v>0.3178355742128724</v>
+        <v>7.9015069853569708E-2</v>
       </c>
       <c r="C95">
         <f t="shared" si="3"/>
-        <v>18.75</v>
-      </c>
-    </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B96">
         <f t="shared" si="2"/>
-        <v>0.31886201520731511</v>
+        <v>8.0917376152326803E-2</v>
       </c>
       <c r="C96">
         <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+        <v>36500</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B97">
         <f t="shared" si="2"/>
-        <v>0.31976303686122226</v>
+        <v>8.2790548899946304E-2</v>
       </c>
       <c r="C97">
         <f t="shared" si="3"/>
-        <v>19.25</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B98">
         <f t="shared" si="2"/>
-        <v>0.32055042067798994</v>
+        <v>8.4632174627258694E-2</v>
       </c>
       <c r="C98">
         <f t="shared" si="3"/>
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+        <v>37500</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B99">
         <f t="shared" si="2"/>
-        <v>0.32123538511752886</v>
+        <v>8.643996630355924E-2</v>
       </c>
       <c r="C99">
         <f t="shared" si="3"/>
-        <v>19.75</v>
-      </c>
-    </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B100">
         <f t="shared" si="2"/>
-        <v>0.32182852889030422</v>
+        <v>8.8211771606171191E-2</v>
       </c>
       <c r="C100">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B101">
         <f t="shared" si="2"/>
-        <v>0.32233978948549169</v>
+        <v>8.9945580379575493E-2</v>
       </c>
       <c r="C101">
         <f t="shared" si="3"/>
-        <v>20.25</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B102">
         <f t="shared" si="2"/>
-        <v>0.32277841604000762</v>
+        <v>9.1639531234810279E-2</v>
       </c>
       <c r="C102">
         <f t="shared" si="3"/>
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+        <v>39500</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B103">
         <f t="shared" si="2"/>
-        <v>0.32315295543592437</v>
+        <v>9.32919172469414E-2</v>
       </c>
       <c r="C103">
         <f t="shared" si="3"/>
-        <v>20.75</v>
-      </c>
-    </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B104">
         <f t="shared" si="2"/>
-        <v>0.32347125034502283</v>
+        <v>9.4901190715968961E-2</v>
       </c>
       <c r="C104">
         <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+        <v>40500</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B105">
         <f t="shared" si="2"/>
-        <v>0.32374044782105788</v>
+        <v>9.6465966964479927E-2</v>
       </c>
       <c r="C105">
         <f t="shared" si="3"/>
-        <v>21.25</v>
-      </c>
-    </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B106">
         <f t="shared" si="2"/>
-        <v>0.32396701697112512</v>
+        <v>9.7985027153597692E-2</v>
       </c>
       <c r="C106">
         <f t="shared" si="3"/>
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+        <v>41500</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B107">
         <f t="shared" si="2"/>
-        <v>0.32415677421421263</v>
+        <v>9.9457320107219804E-2</v>
       </c>
       <c r="C107">
         <f t="shared" si="3"/>
-        <v>21.75</v>
-      </c>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B108">
         <f t="shared" si="2"/>
-        <v>0.32431491465326501</v>
+        <v>0.10088196314308123</v>
       </c>
       <c r="C108">
         <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B109">
         <f t="shared" si="2"/>
-        <v>0.32444604814158295</v>
+        <v>0.10225824191772932</v>
       </c>
       <c r="C109">
         <f t="shared" si="3"/>
-        <v>22.25</v>
-      </c>
-    </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B110">
         <f t="shared" si="2"/>
-        <v>0.3245542387092018</v>
+        <v>0.1035856093009499</v>
       </c>
       <c r="C110">
         <f t="shared" si="3"/>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B111">
         <f t="shared" si="2"/>
-        <v>0.32464304612372757</v>
+        <v>0.10486368330344273</v>
       </c>
       <c r="C111">
         <f t="shared" si="3"/>
-        <v>22.75</v>
-      </c>
-    </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B112">
         <f t="shared" si="2"/>
-        <v>0.32471556848661476</v>
+        <v>0.10609224408950788</v>
       </c>
       <c r="C112">
         <f t="shared" si="3"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B113">
         <f t="shared" si="2"/>
-        <v>0.32477448490384953</v>
+        <v>0.10727123011408218</v>
       </c>
       <c r="C113">
         <f t="shared" si="3"/>
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B114">
         <f t="shared" si="2"/>
-        <v>0.32482209741368234</v>
+        <v>0.10840073343056618</v>
       </c>
       <c r="C114">
         <f t="shared" si="3"/>
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+        <v>45500</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B115">
         <f t="shared" si="2"/>
-        <v>0.32486037149823072</v>
+        <v>0.10948099422242338</v>
       </c>
       <c r="C115">
         <f t="shared" si="3"/>
-        <v>23.75</v>
-      </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B116">
         <f t="shared" si="2"/>
-        <v>0.3248909746459317</v>
+        <v>0.11051239461744319</v>
       </c>
       <c r="C116">
         <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+        <v>46500</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B117">
         <f t="shared" si="2"/>
-        <v>0.32491531256425021</v>
+        <v>0.11149545184876868</v>
       </c>
       <c r="C117">
         <f t="shared" si="3"/>
-        <v>24.25</v>
-      </c>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B118">
         <f t="shared" si="2"/>
-        <v>0.32493456276384014</v>
+        <v>0.11243081083124459</v>
       </c>
       <c r="C118">
         <f t="shared" si="3"/>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+        <v>47500</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B119">
         <f t="shared" si="2"/>
-        <v>0.32494970534441392</v>
+        <v>0.11331923622529684</v>
       </c>
       <c r="C119">
         <f t="shared" si="3"/>
-        <v>24.75</v>
-      </c>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B120">
         <f t="shared" si="2"/>
-        <v>0.32496155090760193</v>
+        <v>0.11416160406337549</v>
       </c>
       <c r="C120">
         <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+        <v>48500</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B121">
         <f t="shared" si="2"/>
-        <v>0.32497076560245858</v>
+        <v>0.11495889301595999</v>
       </c>
       <c r="C121">
         <f t="shared" si="3"/>
-        <v>25.25</v>
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B122">
+        <f t="shared" si="2"/>
+        <v>0.11571217537522674</v>
+      </c>
+      <c r="C122">
+        <f t="shared" si="3"/>
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B123">
+        <f t="shared" si="2"/>
+        <v>0.11642260783471928</v>
+      </c>
+      <c r="C123">
+        <f t="shared" si="3"/>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B124">
+        <f t="shared" si="2"/>
+        <v>0.11709142214275396</v>
+      </c>
+      <c r="C124">
+        <f t="shared" si="3"/>
+        <v>50500</v>
       </c>
     </row>
   </sheetData>
@@ -5378,675 +5404,683 @@
   <sheetPr>
     <tabColor rgb="FF002060"/>
   </sheetPr>
-  <dimension ref="A1:CE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CF2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:83" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
       <c r="B1">
-        <f>(1-EXP(-((B2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
+        <f>(1-EXP(-((B2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
         <v>0</v>
       </c>
       <c r="C1">
-        <f>(1-EXP(-((C2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>2.9387164590499728E-6</v>
+        <f>(1-EXP(-((C2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.1302755611730664E-6</v>
       </c>
       <c r="D1">
-        <f>(1-EXP(-((D2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>2.3508987656584158E-5</v>
+        <f>(1-EXP(-((D2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>9.041918329455445E-6</v>
       </c>
       <c r="E1">
-        <f>(1-EXP(-((E2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>7.9336018158404631E-5</v>
+        <f>(1-EXP(-((E2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>3.0513853137847935E-5</v>
       </c>
       <c r="F1">
-        <f>(1-EXP(-((F2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>1.8802429327882398E-4</v>
+        <f>(1-EXP(-((F2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>7.2317035876470759E-5</v>
       </c>
       <c r="G1">
-        <f>(1-EXP(-((G2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>3.6713369702505162E-4</v>
+        <f>(1-EXP(-((G2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.4120526808655831E-4</v>
       </c>
       <c r="H1">
-        <f>(1-EXP(-((H2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>6.3414614007045462E-4</v>
+        <f>(1-EXP(-((H2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>2.4390236156555944E-4</v>
       </c>
       <c r="I1">
-        <f>(1-EXP(-((I2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>1.006422790718059E-3</v>
+        <f>(1-EXP(-((I2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>3.8708568873771498E-4</v>
       </c>
       <c r="J1">
-        <f>(1-EXP(-((J2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>1.5011520593627675E-3</v>
+        <f>(1-EXP(-((J2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>5.7736617667798751E-4</v>
       </c>
       <c r="K1">
-        <f>(1-EXP(-((K2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>2.1352885583158314E-3</v>
+        <f>(1-EXP(-((K2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>8.2126483012147367E-4</v>
       </c>
       <c r="L1">
-        <f>(1-EXP(-((L2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>2.9254833434584626E-3</v>
+        <f>(1-EXP(-((L2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.1251859013301779E-3</v>
       </c>
       <c r="M1">
-        <f>(1-EXP(-((M2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>3.8880058412656712E-3</v>
+        <f>(1-EXP(-((M2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.4953868620252581E-3</v>
       </c>
       <c r="N1">
-        <f>(1-EXP(-((N2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>5.0386579732422526E-3</v>
+        <f>(1-EXP(-((N2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.9379453743239433E-3</v>
       </c>
       <c r="O1">
-        <f>(1-EXP(-((O2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>6.3926811083940913E-3</v>
+        <f>(1-EXP(-((O2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>2.4587235032284965E-3</v>
       </c>
       <c r="P1">
-        <f>(1-EXP(-((P2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>7.9646566013662247E-3</v>
+        <f>(1-EXP(-((P2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>3.0633294620639323E-3</v>
       </c>
       <c r="Q1">
-        <f>(1-EXP(-((Q2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>9.7684008073131972E-3</v>
+        <f>(1-EXP(-((Q2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>3.7570772335819985E-3</v>
       </c>
       <c r="R1">
-        <f>(1-EXP(-((R2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>1.1816855602081967E-2</v>
+        <f>(1-EXP(-((R2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>4.5449444623392177E-3</v>
       </c>
       <c r="S1">
-        <f>(1-EXP(-((S2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>1.4121975575197189E-2</v>
+        <f>(1-EXP(-((S2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>5.4315290673835337E-3</v>
       </c>
       <c r="T1">
-        <f>(1-EXP(-((T2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>1.6694613200417676E-2</v>
+        <f>(1-EXP(-((T2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>6.4210050770837218E-3</v>
       </c>
       <c r="U1">
-        <f>(1-EXP(-((U2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>1.9544403420951564E-2</v>
+        <f>(1-EXP(-((U2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>7.5170782388275237E-3</v>
       </c>
       <c r="V1">
-        <f>(1-EXP(-((V2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>2.267964921017894E-2</v>
+        <f>(1-EXP(-((V2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>8.7229420039149769E-3</v>
       </c>
       <c r="W1">
-        <f>(1-EXP(-((W2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>2.6107209780122643E-2</v>
+        <f>(1-EXP(-((W2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.0041234530816401E-2</v>
       </c>
       <c r="X1">
-        <f>(1-EXP(-((X2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>2.9832393204970647E-2</v>
+        <f>(1-EXP(-((X2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.1473997386527171E-2</v>
       </c>
       <c r="Y1">
-        <f>(1-EXP(-((Y2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>3.3858855301670994E-2</v>
+        <f>(1-EXP(-((Y2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.3022636654488842E-2</v>
       </c>
       <c r="Z1">
-        <f>(1-EXP(-((Z2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>3.8188506660006477E-2</v>
+        <f>(1-EXP(-((Z2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.4687887176925568E-2</v>
       </c>
       <c r="AA1">
-        <f>(1-EXP(-((AA2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>4.2821429736777793E-2</v>
+        <f>(1-EXP(-((AA2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.6469780667991457E-2</v>
       </c>
       <c r="AB1">
-        <f>(1-EXP(-((AB2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>4.7755807919210802E-2</v>
+        <f>(1-EXP(-((AB2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>1.8367618430465693E-2</v>
       </c>
       <c r="AC1">
-        <f>(1-EXP(-((AC2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>5.2987868418287974E-2</v>
+        <f>(1-EXP(-((AC2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>2.0379949391649221E-2</v>
       </c>
       <c r="AD1">
-        <f>(1-EXP(-((AD2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>5.8511840770746393E-2</v>
+        <f>(1-EXP(-((AD2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>2.2504554142594765E-2</v>
       </c>
       <c r="AE1">
-        <f>(1-EXP(-((AE2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>6.4319932607017835E-2</v>
+        <f>(1-EXP(-((AE2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>2.4738435618083782E-2</v>
       </c>
       <c r="AF1">
-        <f>(1-EXP(-((AF2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>7.040232418023408E-2</v>
+        <f>(1-EXP(-((AF2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>2.7077816992397724E-2</v>
       </c>
       <c r="AG1">
-        <f>(1-EXP(-((AG2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>7.6747182948336296E-2</v>
+        <f>(1-EXP(-((AG2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>2.951814728782165E-2</v>
       </c>
       <c r="AH1">
-        <f>(1-EXP(-((AH2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>8.3340699258080464E-2</v>
+        <f>(1-EXP(-((AH2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>3.2054115099261718E-2</v>
       </c>
       <c r="AI1">
-        <f>(1-EXP(-((AI2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>9.0167143898212704E-2</v>
+        <f>(1-EXP(-((AI2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>3.467967073008181E-2</v>
       </c>
       <c r="AJ1">
-        <f>(1-EXP(-((AJ2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>9.7208947972360321E-2</v>
+        <f>(1-EXP(-((AJ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>3.7388056912446274E-2</v>
       </c>
       <c r="AK1">
-        <f>(1-EXP(-((AK2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.10444680519450757</v>
+        <f>(1-EXP(-((AK2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>4.0171848151733677E-2</v>
       </c>
       <c r="AL1">
-        <f>(1-EXP(-((AL2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.11185979633676199</v>
+        <f>(1-EXP(-((AL2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>4.3022998591062303E-2</v>
       </c>
       <c r="AM1">
-        <f>(1-EXP(-((AM2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.11942553516706651</v>
+        <f>(1-EXP(-((AM2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>4.5932898141179429E-2</v>
       </c>
       <c r="AN1">
-        <f>(1-EXP(-((AN2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.12712033481123883</v>
+        <f>(1-EXP(-((AN2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>4.8892436465861083E-2</v>
       </c>
       <c r="AO1">
-        <f>(1-EXP(-((AO2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.13491939306780171</v>
+        <f>(1-EXP(-((AO2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>5.1892074256846804E-2</v>
       </c>
       <c r="AP1">
-        <f>(1-EXP(-((AP2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.14279699480482452</v>
+        <f>(1-EXP(-((AP2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>5.4921921078778663E-2</v>
       </c>
       <c r="AQ1">
-        <f>(1-EXP(-((AQ2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.15072672918526989</v>
+        <f>(1-EXP(-((AQ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>5.7971818917411488E-2</v>
       </c>
       <c r="AR1">
-        <f>(1-EXP(-((AR2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.15868171911122922</v>
+        <f>(1-EXP(-((AR2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>6.1031430427395852E-2</v>
       </c>
       <c r="AS1">
-        <f>(1-EXP(-((AS2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.16663485995800573</v>
+        <f>(1-EXP(-((AS2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>6.4090330753079128E-2</v>
       </c>
       <c r="AT1">
-        <f>(1-EXP(-((AT2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.17455906439599175</v>
+        <f>(1-EXP(-((AT2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>6.7138101690766061E-2</v>
       </c>
       <c r="AU1">
-        <f>(1-EXP(-((AU2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.18242750988073522</v>
+        <f>(1-EXP(-((AU2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>7.0164426877205852E-2</v>
       </c>
       <c r="AV1">
-        <f>(1-EXP(-((AV2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.19021388523755758</v>
+        <f>(1-EXP(-((AV2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>7.3159186629829842E-2</v>
       </c>
       <c r="AW1">
-        <f>(1-EXP(-((AW2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.19789263268329291</v>
+        <f>(1-EXP(-((AW2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>7.6112551032035736E-2</v>
       </c>
       <c r="AX1">
-        <f>(1-EXP(-((AX2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.20543918161928124</v>
+        <f>(1-EXP(-((AX2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>7.9015069853569708E-2</v>
       </c>
       <c r="AY1">
-        <f>(1-EXP(-((AY2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.21283017059990736</v>
+        <f>(1-EXP(-((AY2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>8.1857757923041286E-2</v>
       </c>
       <c r="AZ1">
-        <f>(1-EXP(-((AZ2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.22004365403087262</v>
+        <f>(1-EXP(-((AZ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>8.4632174627258694E-2</v>
       </c>
       <c r="BA1">
-        <f>(1-EXP(-((BA2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.22705929037995962</v>
+        <f>(1-EXP(-((BA2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>8.7330496299984461E-2</v>
       </c>
       <c r="BB1">
-        <f>(1-EXP(-((BB2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.23385850898689628</v>
+        <f>(1-EXP(-((BB2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>8.9945580379575493E-2</v>
       </c>
       <c r="BC1">
-        <f>(1-EXP(-((BC2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.24042465293238419</v>
+        <f>(1-EXP(-((BC2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>9.2471020358609296E-2</v>
       </c>
       <c r="BD1">
-        <f>(1-EXP(-((BD2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.2467430958615193</v>
+        <f>(1-EXP(-((BD2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>9.4901190715968961E-2</v>
       </c>
       <c r="BE1">
-        <f>(1-EXP(-((BE2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.25280133114377951</v>
+        <f>(1-EXP(-((BE2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>9.7231281209145953E-2</v>
       </c>
       <c r="BF1">
-        <f>(1-EXP(-((BF2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.2585890322787715</v>
+        <f>(1-EXP(-((BF2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>9.9457320107219804E-2</v>
       </c>
       <c r="BG1">
-        <f>(1-EXP(-((BG2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.26409808401086282</v>
+        <f>(1-EXP(-((BG2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.10157618615802415</v>
       </c>
       <c r="BH1">
-        <f>(1-EXP(-((BH2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.26932258418246974</v>
+        <f>(1-EXP(-((BH2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.1035856093009499</v>
       </c>
       <c r="BI1">
-        <f>(1-EXP(-((BI2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.27425881692032672</v>
+        <f>(1-EXP(-((BI2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.10548416035397182</v>
       </c>
       <c r="BJ1">
-        <f>(1-EXP(-((BJ2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.2789051982966137</v>
+        <f>(1-EXP(-((BJ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.10727123011408218</v>
       </c>
       <c r="BK1">
-        <f>(1-EXP(-((BK2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.28326219612285092</v>
+        <f>(1-EXP(-((BK2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.10894699850878881</v>
       </c>
       <c r="BL1">
-        <f>(1-EXP(-((BL2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.2873322260053523</v>
+        <f>(1-EXP(-((BL2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.11051239461744319</v>
       </c>
       <c r="BM1">
-        <f>(1-EXP(-((BM2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.29111952620450759</v>
+        <f>(1-EXP(-((BM2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.11196904854019522</v>
       </c>
       <c r="BN1">
-        <f>(1-EXP(-((BN2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.29463001418577178</v>
+        <f>(1-EXP(-((BN2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.11331923622529684</v>
       </c>
       <c r="BO1">
-        <f>(1-EXP(-((BO2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.29787112801967686</v>
+        <f>(1-EXP(-((BO2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.11456581846910648</v>
       </c>
       <c r="BP1">
-        <f>(1-EXP(-((BP2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.30085165597558955</v>
+        <f>(1-EXP(-((BP2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.11571217537522674</v>
       </c>
       <c r="BQ1">
-        <f>(1-EXP(-((BQ2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.30358155775609158</v>
+        <f>(1-EXP(-((BQ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.11676213759849677</v>
       </c>
       <c r="BR1">
-        <f>(1-EXP(-((BR2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.30607178083525383</v>
+        <f>(1-EXP(-((BR2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.11771991570586685</v>
       </c>
       <c r="BS1">
-        <f>(1-EXP(-((BS2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.30833407529690587</v>
+        <f>(1-EXP(-((BS2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.11859002896034841</v>
       </c>
       <c r="BT1">
-        <f>(1-EXP(-((BT2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.31038081042304033</v>
+        <f>(1-EXP(-((BT2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.11937723477809242</v>
       </c>
       <c r="BU1">
-        <f>(1-EXP(-((BU2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.31222479606484704</v>
+        <f>(1-EXP(-((BU2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12008646002494117</v>
       </c>
       <c r="BV1">
-        <f>(1-EXP(-((BV2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.31387911154870857</v>
+        <f>(1-EXP(-((BV2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12072273521104175</v>
       </c>
       <c r="BW1">
-        <f>(1-EXP(-((BW2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.31535694453758484</v>
+        <f>(1-EXP(-((BW2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12129113251445571</v>
       </c>
       <c r="BX1">
-        <f>(1-EXP(-((BX2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.31667144189658553</v>
+        <f>(1-EXP(-((BX2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12179670842176366</v>
       </c>
       <c r="BY1">
-        <f>(1-EXP(-((BY2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.3178355742128724</v>
+        <f>(1-EXP(-((BY2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12224445162033554</v>
       </c>
       <c r="BZ1">
-        <f>(1-EXP(-((BZ2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.31886201520731511</v>
+        <f>(1-EXP(-((BZ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12263923661819812</v>
       </c>
       <c r="CA1">
-        <f>(1-EXP(-((CA2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.31976303686122226</v>
+        <f>(1-EXP(-((CA2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12298578340816241</v>
       </c>
       <c r="CB1">
-        <f>(1-EXP(-((CB2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.32055042067798994</v>
+        <f>(1-EXP(-((CB2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12328862333768843</v>
       </c>
       <c r="CC1">
-        <f>(1-EXP(-((CC2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.32123538511752886</v>
+        <f>(1-EXP(-((CC2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12355207119904957</v>
       </c>
       <c r="CD1">
-        <f>(1-EXP(-((CD2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.32182852889030422</v>
+        <f>(1-EXP(-((CD2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.12378020341934777</v>
       </c>
       <c r="CE1">
-        <f>(1-EXP(-((CE2/About!$B$16-(About!$B$15-0.5))/About!$B$13)^About!$B$14))*About!$B$12</f>
-        <v>0.32500000000000001</v>
-      </c>
-    </row>
-    <row r="2" spans="1:83" x14ac:dyDescent="0.25">
+        <f>(1-EXP(-((CE2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.1239768421098045</v>
+      </c>
+      <c r="CF1">
+        <f>(1-EXP(-((CF2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:84" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <f>B2+0.25</f>
-        <v>0.25</v>
+        <f>B2+750</f>
+        <v>750</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:AI2" si="0">C2+0.25</f>
-        <v>0.5</v>
+        <f t="shared" ref="D2:BO2" si="0">C2+750</f>
+        <v>1500</v>
       </c>
       <c r="E2">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>2250</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>1.25</v>
+        <v>3750</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>4500</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>5250</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>6000</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>6750</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>7500</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>2.75</v>
+        <v>8250</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>9000</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>3.25</v>
+        <v>9750</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>10500</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>3.75</v>
+        <v>11250</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>12000</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>4.25</v>
+        <v>12750</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>13500</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>4.75</v>
+        <v>14250</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>15000</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>5.25</v>
+        <v>15750</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>16500</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>5.75</v>
+        <v>17250</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>18000</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>6.25</v>
+        <v>18750</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>19500</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>6.75</v>
+        <v>20250</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>21000</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>7.25</v>
+        <v>21750</v>
       </c>
       <c r="AF2">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>22500</v>
       </c>
       <c r="AG2">
         <f t="shared" si="0"/>
-        <v>7.75</v>
+        <v>23250</v>
       </c>
       <c r="AH2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>24000</v>
       </c>
       <c r="AI2">
         <f t="shared" si="0"/>
-        <v>8.25</v>
+        <v>24750</v>
       </c>
       <c r="AJ2">
-        <f>AI2+0.25</f>
-        <v>8.5</v>
+        <f t="shared" si="0"/>
+        <v>25500</v>
       </c>
       <c r="AK2">
-        <f t="shared" ref="AK2:AO2" si="1">AJ2+0.25</f>
-        <v>8.75</v>
+        <f t="shared" si="0"/>
+        <v>26250</v>
       </c>
       <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>27000</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>27750</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>28500</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>29250</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>30750</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>31500</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>32250</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>33000</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>33750</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>34500</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>35250</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>36000</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>36750</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>37500</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="0"/>
+        <v>38250</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="0"/>
+        <v>39000</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="0"/>
+        <v>39750</v>
+      </c>
+      <c r="BD2">
+        <f t="shared" si="0"/>
+        <v>40500</v>
+      </c>
+      <c r="BE2">
+        <f t="shared" si="0"/>
+        <v>41250</v>
+      </c>
+      <c r="BF2">
+        <f t="shared" si="0"/>
+        <v>42000</v>
+      </c>
+      <c r="BG2">
+        <f t="shared" si="0"/>
+        <v>42750</v>
+      </c>
+      <c r="BH2">
+        <f t="shared" si="0"/>
+        <v>43500</v>
+      </c>
+      <c r="BI2">
+        <f t="shared" si="0"/>
+        <v>44250</v>
+      </c>
+      <c r="BJ2">
+        <f t="shared" si="0"/>
+        <v>45000</v>
+      </c>
+      <c r="BK2">
+        <f t="shared" si="0"/>
+        <v>45750</v>
+      </c>
+      <c r="BL2">
+        <f t="shared" si="0"/>
+        <v>46500</v>
+      </c>
+      <c r="BM2">
+        <f t="shared" si="0"/>
+        <v>47250</v>
+      </c>
+      <c r="BN2">
+        <f t="shared" si="0"/>
+        <v>48000</v>
+      </c>
+      <c r="BO2">
+        <f t="shared" si="0"/>
+        <v>48750</v>
+      </c>
+      <c r="BP2">
+        <f t="shared" ref="BP2:CE2" si="1">BO2+750</f>
+        <v>49500</v>
+      </c>
+      <c r="BQ2">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="AM2">
+        <v>50250</v>
+      </c>
+      <c r="BR2">
         <f t="shared" si="1"/>
-        <v>9.25</v>
-      </c>
-      <c r="AN2">
+        <v>51000</v>
+      </c>
+      <c r="BS2">
         <f t="shared" si="1"/>
-        <v>9.5</v>
-      </c>
-      <c r="AO2">
+        <v>51750</v>
+      </c>
+      <c r="BT2">
         <f t="shared" si="1"/>
-        <v>9.75</v>
-      </c>
-      <c r="AP2">
-        <f>AO2+0.25</f>
-        <v>10</v>
-      </c>
-      <c r="AQ2">
-        <f t="shared" ref="AQ2:BJ2" si="2">AP2+0.25</f>
-        <v>10.25</v>
-      </c>
-      <c r="AR2">
-        <f t="shared" si="2"/>
-        <v>10.5</v>
-      </c>
-      <c r="AS2">
-        <f t="shared" si="2"/>
-        <v>10.75</v>
-      </c>
-      <c r="AT2">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="AU2">
-        <f t="shared" si="2"/>
-        <v>11.25</v>
-      </c>
-      <c r="AV2">
-        <f t="shared" si="2"/>
-        <v>11.5</v>
-      </c>
-      <c r="AW2">
-        <f t="shared" si="2"/>
-        <v>11.75</v>
-      </c>
-      <c r="AX2">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="AY2">
-        <f t="shared" si="2"/>
-        <v>12.25</v>
-      </c>
-      <c r="AZ2">
-        <f t="shared" si="2"/>
-        <v>12.5</v>
-      </c>
-      <c r="BA2">
-        <f t="shared" si="2"/>
-        <v>12.75</v>
-      </c>
-      <c r="BB2">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="BC2">
-        <f t="shared" si="2"/>
-        <v>13.25</v>
-      </c>
-      <c r="BD2">
-        <f t="shared" si="2"/>
-        <v>13.5</v>
-      </c>
-      <c r="BE2">
-        <f t="shared" si="2"/>
-        <v>13.75</v>
-      </c>
-      <c r="BF2">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="BG2">
-        <f t="shared" si="2"/>
-        <v>14.25</v>
-      </c>
-      <c r="BH2">
-        <f t="shared" si="2"/>
-        <v>14.5</v>
-      </c>
-      <c r="BI2">
-        <f t="shared" si="2"/>
-        <v>14.75</v>
-      </c>
-      <c r="BJ2">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="BK2">
-        <f t="shared" ref="BK2" si="3">BJ2+0.25</f>
-        <v>15.25</v>
-      </c>
-      <c r="BL2">
-        <f t="shared" ref="BL2" si="4">BK2+0.25</f>
-        <v>15.5</v>
-      </c>
-      <c r="BM2">
-        <f t="shared" ref="BM2" si="5">BL2+0.25</f>
-        <v>15.75</v>
-      </c>
-      <c r="BN2">
-        <f t="shared" ref="BN2" si="6">BM2+0.25</f>
-        <v>16</v>
-      </c>
-      <c r="BO2">
-        <f t="shared" ref="BO2" si="7">BN2+0.25</f>
-        <v>16.25</v>
-      </c>
-      <c r="BP2">
-        <f t="shared" ref="BP2" si="8">BO2+0.25</f>
-        <v>16.5</v>
-      </c>
-      <c r="BQ2">
-        <f t="shared" ref="BQ2" si="9">BP2+0.25</f>
-        <v>16.75</v>
-      </c>
-      <c r="BR2">
-        <f t="shared" ref="BR2" si="10">BQ2+0.25</f>
-        <v>17</v>
-      </c>
-      <c r="BS2">
-        <f t="shared" ref="BS2" si="11">BR2+0.25</f>
-        <v>17.25</v>
-      </c>
-      <c r="BT2">
-        <f t="shared" ref="BT2" si="12">BS2+0.25</f>
-        <v>17.5</v>
+        <v>52500</v>
       </c>
       <c r="BU2">
-        <f t="shared" ref="BU2" si="13">BT2+0.25</f>
-        <v>17.75</v>
+        <f t="shared" si="1"/>
+        <v>53250</v>
       </c>
       <c r="BV2">
-        <f t="shared" ref="BV2" si="14">BU2+0.25</f>
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>54000</v>
       </c>
       <c r="BW2">
-        <f t="shared" ref="BW2" si="15">BV2+0.25</f>
-        <v>18.25</v>
+        <f t="shared" si="1"/>
+        <v>54750</v>
       </c>
       <c r="BX2">
-        <f t="shared" ref="BX2" si="16">BW2+0.25</f>
-        <v>18.5</v>
+        <f t="shared" si="1"/>
+        <v>55500</v>
       </c>
       <c r="BY2">
-        <f t="shared" ref="BY2" si="17">BX2+0.25</f>
-        <v>18.75</v>
+        <f t="shared" si="1"/>
+        <v>56250</v>
       </c>
       <c r="BZ2">
-        <f t="shared" ref="BZ2" si="18">BY2+0.25</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>57000</v>
       </c>
       <c r="CA2">
-        <f t="shared" ref="CA2" si="19">BZ2+0.25</f>
-        <v>19.25</v>
+        <f t="shared" si="1"/>
+        <v>57750</v>
       </c>
       <c r="CB2">
-        <f t="shared" ref="CB2" si="20">CA2+0.25</f>
-        <v>19.5</v>
+        <f t="shared" si="1"/>
+        <v>58500</v>
       </c>
       <c r="CC2">
-        <f t="shared" ref="CC2" si="21">CB2+0.25</f>
-        <v>19.75</v>
+        <f t="shared" si="1"/>
+        <v>59250</v>
       </c>
       <c r="CD2">
-        <f t="shared" ref="CD2" si="22">CC2+0.25</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>60000</v>
       </c>
       <c r="CE2">
-        <v>1000</v>
+        <f t="shared" si="1"/>
+        <v>60750</v>
+      </c>
+      <c r="CF2" s="2">
+        <v>1000000</v>
       </c>
     </row>
   </sheetData>
@@ -6061,19 +6095,19 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="B2">
         <v>0.02</v>
@@ -6090,12 +6124,12 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -6190,7 +6224,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -6285,7 +6319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6380,7 +6414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -6475,7 +6509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6570,7 +6604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -6665,102 +6699,102 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Z7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AB7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AC7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AD7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AE7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -6855,7 +6889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6950,7 +6984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -7045,7 +7079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -7140,7 +7174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7235,7 +7269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -7330,7 +7364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -7425,7 +7459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -7520,7 +7554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -7615,7 +7649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -7710,7 +7744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -7805,7 +7839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -7900,7 +7934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -7995,7 +8029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -8090,7 +8124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -8185,7 +8219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -8280,7 +8314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -8375,7 +8409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>

--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C208883-69A2-4C97-8CB4-4A540A7A8C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6367CB4D-9140-4286-9A37-2062052CD2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -214,10 +214,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -307,307 +306,307 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>500</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1000</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1500</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2500</c:v>
+                  <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3000</c:v>
+                  <c:v>1.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3500</c:v>
+                  <c:v>1.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4500</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5000</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5500</c:v>
+                  <c:v>2.75</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>6000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6500</c:v>
+                  <c:v>3.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7000</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7500</c:v>
+                  <c:v>3.75</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>8500</c:v>
+                  <c:v>4.25</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>9000</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>9500</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>10000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>10500</c:v>
+                  <c:v>5.25</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>11000</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>11500</c:v>
+                  <c:v>5.75</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>12000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>12500</c:v>
+                  <c:v>6.25</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>13000</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>13500</c:v>
+                  <c:v>6.75</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>14000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>14500</c:v>
+                  <c:v>7.25</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>15000</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>15500</c:v>
+                  <c:v>7.75</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>16000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>16500</c:v>
+                  <c:v>8.25</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>17000</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>17500</c:v>
+                  <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>18000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>18500</c:v>
+                  <c:v>9.25</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>19000</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>19500</c:v>
+                  <c:v>9.75</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>20000</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>20500</c:v>
+                  <c:v>10.25</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>21000</c:v>
+                  <c:v>10.5</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>21500</c:v>
+                  <c:v>10.75</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>22000</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>22500</c:v>
+                  <c:v>11.25</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>23000</c:v>
+                  <c:v>11.5</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>23500</c:v>
+                  <c:v>11.75</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>24000</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>24500</c:v>
+                  <c:v>12.25</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>25000</c:v>
+                  <c:v>12.5</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>25500</c:v>
+                  <c:v>12.75</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>26000</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>26500</c:v>
+                  <c:v>13.25</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>27000</c:v>
+                  <c:v>13.5</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>27500</c:v>
+                  <c:v>13.75</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>28000</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>28500</c:v>
+                  <c:v>14.25</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>29000</c:v>
+                  <c:v>14.5</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>29500</c:v>
+                  <c:v>14.75</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>30000</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>30500</c:v>
+                  <c:v>15.25</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>31000</c:v>
+                  <c:v>15.5</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>31500</c:v>
+                  <c:v>15.75</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>32000</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>32500</c:v>
+                  <c:v>16.25</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>33000</c:v>
+                  <c:v>16.5</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>33500</c:v>
+                  <c:v>16.75</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>34000</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>34500</c:v>
+                  <c:v>17.25</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>35000</c:v>
+                  <c:v>17.5</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>35500</c:v>
+                  <c:v>17.75</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>36000</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>36500</c:v>
+                  <c:v>18.25</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>37000</c:v>
+                  <c:v>18.5</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>37500</c:v>
+                  <c:v>18.75</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>38000</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>38500</c:v>
+                  <c:v>19.25</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>39000</c:v>
+                  <c:v>19.5</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>39500</c:v>
+                  <c:v>19.75</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>40000</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>40500</c:v>
+                  <c:v>20.25</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>41000</c:v>
+                  <c:v>20.5</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>41500</c:v>
+                  <c:v>20.75</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>42000</c:v>
+                  <c:v>21</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>42500</c:v>
+                  <c:v>21.25</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>43000</c:v>
+                  <c:v>21.5</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>43500</c:v>
+                  <c:v>21.75</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>44000</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>44500</c:v>
+                  <c:v>22.25</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>45000</c:v>
+                  <c:v>22.5</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>45500</c:v>
+                  <c:v>22.75</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>46000</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>46500</c:v>
+                  <c:v>23.25</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>47000</c:v>
+                  <c:v>23.5</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>47500</c:v>
+                  <c:v>23.75</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>48000</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>48500</c:v>
+                  <c:v>24.25</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>49000</c:v>
+                  <c:v>24.5</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>49500</c:v>
+                  <c:v>24.75</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>50000</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>50500</c:v>
+                  <c:v>25.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -619,307 +618,307 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>3.3489752805648809E-7</c:v>
+                  <c:v>1.1302755611730664E-6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.6791551015481474E-6</c:v>
+                  <c:v>9.041918329455445E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.041918329455445E-6</c:v>
+                  <c:v>3.0513853137847935E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.1431633037929942E-5</c:v>
+                  <c:v>7.2317035876470759E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.1855238076579648E-5</c:v>
+                  <c:v>1.4120526808655831E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.2317035876470759E-5</c:v>
+                  <c:v>2.4390236156555944E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.1481724169225271E-4</c:v>
+                  <c:v>3.8708568873771498E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.7135021303994746E-4</c:v>
+                  <c:v>5.7736617667798751E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.4390236156555944E-4</c:v>
+                  <c:v>8.2126483012147367E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.3444975044409631E-4</c:v>
+                  <c:v>1.1251859013301779E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4.4495538141219038E-4</c:v>
+                  <c:v>1.4953868620252581E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.7736617667798751E-4</c:v>
+                  <c:v>1.9379453743239433E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.336096622230226E-4</c:v>
+                  <c:v>2.4587235032284965E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9.1559036041015396E-4</c:v>
+                  <c:v>3.0633294620639323E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.1251859013301779E-3</c:v>
+                  <c:v>3.7570772335819985E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.3642428639517451E-3</c:v>
+                  <c:v>4.5449444623392177E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.6345723598757272E-3</c:v>
+                  <c:v>5.4315290673835337E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.9379453743239433E-3</c:v>
+                  <c:v>6.4210050770837218E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.2760878809044566E-3</c:v>
+                  <c:v>7.5170782388275237E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.6506757486755017E-3</c:v>
+                  <c:v>8.7229420039149769E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>3.0633294620639323E-3</c:v>
+                  <c:v>1.0041234530816401E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>3.5156086762653666E-3</c:v>
+                  <c:v>1.1473997386527171E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.0090066328439117E-3</c:v>
+                  <c:v>1.3022636654488842E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>4.5449444623392177E-3</c:v>
+                  <c:v>1.4687887176925568E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>5.1247654027590517E-3</c:v>
+                  <c:v>1.6469780667991457E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>5.7497289648605621E-3</c:v>
+                  <c:v>1.8367618430465693E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.4210050770837218E-3</c:v>
+                  <c:v>2.0379949391649221E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>7.139668244867739E-3</c:v>
+                  <c:v>2.2504554142594765E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7.9066917608325293E-3</c:v>
+                  <c:v>2.4738435618083782E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>8.7229420039149769E-3</c:v>
+                  <c:v>2.7077816992397724E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9.5891728669876136E-3</c:v>
+                  <c:v>2.951814728782165E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.0506020353728399E-2</c:v>
+                  <c:v>3.2054115099261718E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>1.1473997386527171E-2</c:v>
+                  <c:v>3.467967073008181E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.2493488867981531E-2</c:v>
+                  <c:v>3.7388056912446274E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.3564747039025687E-2</c:v>
+                  <c:v>4.0171848151733677E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.4687887176925568E-2</c:v>
+                  <c:v>4.3022998591062303E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.5862883676240225E-2</c:v>
+                  <c:v>4.5932898141179429E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.7089566555369529E-2</c:v>
+                  <c:v>4.8892436465861083E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.8367618430465693E-2</c:v>
+                  <c:v>5.1892074256846804E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.9696571997260381E-2</c:v>
+                  <c:v>5.4921921078778663E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>2.1075808059742129E-2</c:v>
+                  <c:v>5.7971818917411488E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>2.2504554142594765E-2</c:v>
+                  <c:v>6.1031430427395852E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>2.3981883721876138E-2</c:v>
+                  <c:v>6.4090330753079128E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>2.5506716105570884E-2</c:v>
+                  <c:v>6.7138101690766061E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>2.7077816992397724E-2</c:v>
+                  <c:v>7.0164426877205852E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>2.8693799733595995E-2</c:v>
+                  <c:v>7.3159186629829842E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>3.035312731837099E-2</c:v>
+                  <c:v>7.6112551032035736E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>3.2054115099261718E-2</c:v>
+                  <c:v>7.9015069853569708E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>3.3794934268928725E-2</c:v>
+                  <c:v>8.1857757923041286E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>3.5573616094775717E-2</c:v>
+                  <c:v>8.4632174627258694E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>3.7388056912446274E-2</c:v>
+                  <c:v>8.7330496299984461E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>3.9236023873619186E-2</c:v>
+                  <c:v>8.9945580379575493E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>4.1115161437703815E-2</c:v>
+                  <c:v>9.2471020358609296E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>4.3022998591062303E-2</c:v>
+                  <c:v>9.4901190715968961E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>4.495695677130844E-2</c:v>
+                  <c:v>9.7231281209145953E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>4.6914358468115175E-2</c:v>
+                  <c:v>9.9457320107219804E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>4.8892436465861083E-2</c:v>
+                  <c:v>0.10157618615802415</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>5.0888343687428006E-2</c:v>
+                  <c:v>0.1035856093009499</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>5.2899163592589921E-2</c:v>
+                  <c:v>0.10548416035397182</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>5.4921921078778663E-2</c:v>
+                  <c:v>0.10727123011408218</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>5.6953593826638713E-2</c:v>
+                  <c:v>0.10894699850878881</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>5.8991124027762909E-2</c:v>
+                  <c:v>0.11051239461744319</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>6.1031430427395852E-2</c:v>
+                  <c:v>0.11196904854019522</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>6.3071420610770493E-2</c:v>
+                  <c:v>0.11331923622529684</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>6.5108003458162492E-2</c:v>
+                  <c:v>0.11456581846910648</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>6.7138101690766061E-2</c:v>
+                  <c:v>0.11571217537522674</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>6.915866442716484E-2</c:v>
+                  <c:v>0.11676213759849677</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>7.1166679668536584E-2</c:v>
+                  <c:v>0.11771991570586685</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>7.3159186629829842E-2</c:v>
+                  <c:v>0.11859002896034841</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>7.5133287834015461E-2</c:v>
+                  <c:v>0.11937723477809242</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>7.7086160887166397E-2</c:v>
+                  <c:v>0.12008646002494117</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>7.9015069853569708E-2</c:v>
+                  <c:v>0.12072273521104175</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>8.0917376152326803E-2</c:v>
+                  <c:v>0.12129113251445571</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>8.2790548899946304E-2</c:v>
+                  <c:v>0.12179670842176366</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>8.4632174627258694E-2</c:v>
+                  <c:v>0.12224445162033554</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>8.643996630355924E-2</c:v>
+                  <c:v>0.12263923661819812</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>8.8211771606171191E-2</c:v>
+                  <c:v>0.12298578340816241</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>8.9945580379575493E-2</c:v>
+                  <c:v>0.12328862333768843</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>9.1639531234810279E-2</c:v>
+                  <c:v>0.12355207119904957</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>9.32919172469414E-2</c:v>
+                  <c:v>0.12378020341934777</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>9.4901190715968961E-2</c:v>
+                  <c:v>0.1239768421098045</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>9.6465966964479927E-2</c:v>
+                  <c:v>0.12414554463077215</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>9.7985027153597692E-2</c:v>
+                  <c:v>0.12428959824458628</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>9.9457320107219804E-2</c:v>
+                  <c:v>0.12441201936347031</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.10088196314308123</c:v>
+                  <c:v>0.12451555685425303</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.10225824191772932</c:v>
+                  <c:v>0.12460269883504811</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.1035856093009499</c:v>
+                  <c:v>0.12467568239008178</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.10486368330344273</c:v>
+                  <c:v>0.12473650563587114</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.10609224408950788</c:v>
+                  <c:v>0.12478694159291652</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.10727123011408218</c:v>
+                  <c:v>0.12482855334969299</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.10840073343056618</c:v>
+                  <c:v>0.12486271004758752</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.10948099422242338</c:v>
+                  <c:v>0.12489060326408261</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.11051239461744319</c:v>
+                  <c:v>0.12491326342455751</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.11149545184876868</c:v>
+                  <c:v>0.12493157592833935</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.11243081083124459</c:v>
+                  <c:v>0.12494629673008874</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.11331923622529684</c:v>
+                  <c:v>0.12495806717151219</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.11416160406337549</c:v>
+                  <c:v>0.12496742790932699</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.11495889301595999</c:v>
+                  <c:v>0.1249748318322462</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.11571217537522674</c:v>
+                  <c:v>0.12498065590169766</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.11642260783471928</c:v>
+                  <c:v>0.12498521188753921</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.11709142214275396</c:v>
+                  <c:v>0.1249887560009456</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1076,7 +1075,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1084,6 +1082,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1205,124 +1204,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>750</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1500</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2250</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3750</c:v>
+                  <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4500</c:v>
+                  <c:v>1.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5250</c:v>
+                  <c:v>1.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6750</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7500</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8250</c:v>
+                  <c:v>2.75</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9750</c:v>
+                  <c:v>3.25</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>10500</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>11250</c:v>
+                  <c:v>3.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>12750</c:v>
+                  <c:v>4.25</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>13500</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>14250</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>15000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>15750</c:v>
+                  <c:v>5.25</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>16500</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>17250</c:v>
+                  <c:v>5.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>18750</c:v>
+                  <c:v>6.25</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>19500</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>20250</c:v>
+                  <c:v>6.75</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>21000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>21750</c:v>
+                  <c:v>7.25</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>22500</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>23250</c:v>
+                  <c:v>7.75</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>24000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>24750</c:v>
+                  <c:v>8.25</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>25500</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>26250</c:v>
+                  <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>27000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>27750</c:v>
+                  <c:v>9.25</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>28500</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>29250</c:v>
+                  <c:v>9.75</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>30000</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1611,7 +1610,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1619,6 +1617,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1740,124 +1739,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>750</c:v>
+                  <c:v>0.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1500</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2250</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3000</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3750</c:v>
+                  <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4500</c:v>
+                  <c:v>1.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5250</c:v>
+                  <c:v>1.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6000</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6750</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7500</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>8250</c:v>
+                  <c:v>2.75</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9000</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>9750</c:v>
+                  <c:v>3.25</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>10500</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>11250</c:v>
+                  <c:v>3.75</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12000</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>12750</c:v>
+                  <c:v>4.25</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>13500</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>14250</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>15000</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>15750</c:v>
+                  <c:v>5.25</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>16500</c:v>
+                  <c:v>5.5</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>17250</c:v>
+                  <c:v>5.75</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18000</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>18750</c:v>
+                  <c:v>6.25</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>19500</c:v>
+                  <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>20250</c:v>
+                  <c:v>6.75</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>21000</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>21750</c:v>
+                  <c:v>7.25</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>22500</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>23250</c:v>
+                  <c:v>7.75</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>24000</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>24750</c:v>
+                  <c:v>8.25</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>25500</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>26250</c:v>
+                  <c:v>8.75</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>27000</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>27750</c:v>
+                  <c:v>9.25</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>28500</c:v>
+                  <c:v>9.5</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>29250</c:v>
+                  <c:v>9.75</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>30000</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2146,7 +2145,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2154,6 +2152,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4274,28 +4273,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3D2DEE-686E-48A0-AC3D-0F54DEA5D0EC}">
   <dimension ref="A1:C124"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="88.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="88.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -4303,40 +4302,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -4344,7 +4343,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -4352,7 +4351,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -4360,7 +4359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -4368,15 +4367,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
       <c r="B19">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23">
         <f>(1-EXP(-((C23/$B$19-($B$18-0.5))/$B$16)^$B$17))*$B$15</f>
         <v>0</v>
@@ -4385,1012 +4384,1014 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24">
         <f t="shared" ref="B24:B87" si="0">(1-EXP(-((C24/$B$19-($B$18-0.5))/$B$16)^$B$17))*$B$15</f>
-        <v>3.3489752805648809E-7</v>
+        <v>1.1302755611730664E-6</v>
       </c>
       <c r="C24">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+        <f>C23+0.25</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B25">
         <f t="shared" si="0"/>
-        <v>2.6791551015481474E-6</v>
+        <v>9.041918329455445E-6</v>
       </c>
       <c r="C25">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+        <f t="shared" ref="C25:C88" si="1">C24+0.25</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26">
         <f t="shared" si="0"/>
-        <v>9.041918329455445E-6</v>
+        <v>3.0513853137847935E-5</v>
       </c>
       <c r="C26">
-        <f>C25+500</f>
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B27">
         <f t="shared" si="0"/>
-        <v>2.1431633037929942E-5</v>
+        <v>7.2317035876470759E-5</v>
       </c>
       <c r="C27">
-        <f t="shared" ref="C27:C90" si="1">C26+500</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>4.1855238076579648E-5</v>
+        <v>1.4120526808655831E-4</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B29">
         <f t="shared" si="0"/>
-        <v>7.2317035876470759E-5</v>
+        <v>2.4390236156555944E-4</v>
       </c>
       <c r="C29">
         <f t="shared" si="1"/>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B30">
         <f t="shared" si="0"/>
-        <v>1.1481724169225271E-4</v>
+        <v>3.8708568873771498E-4</v>
       </c>
       <c r="C30">
         <f t="shared" si="1"/>
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>1.7135021303994746E-4</v>
+        <v>5.7736617667798751E-4</v>
       </c>
       <c r="C31">
         <f t="shared" si="1"/>
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32">
         <f t="shared" si="0"/>
-        <v>2.4390236156555944E-4</v>
+        <v>8.2126483012147367E-4</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>3.3444975044409631E-4</v>
+        <v>1.1251859013301779E-3</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>4.4495538141219038E-4</v>
+        <v>1.4953868620252581E-3</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35">
         <f t="shared" si="0"/>
-        <v>5.7736617667798751E-4</v>
+        <v>1.9379453743239433E-3</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>7.336096622230226E-4</v>
+        <v>2.4587235032284965E-3</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37">
         <f t="shared" si="0"/>
-        <v>9.1559036041015396E-4</v>
+        <v>3.0633294620639323E-3</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38">
         <f t="shared" si="0"/>
-        <v>1.1251859013301779E-3</v>
+        <v>3.7570772335819985E-3</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39">
         <f t="shared" si="0"/>
-        <v>1.3642428639517451E-3</v>
+        <v>4.5449444623392177E-3</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
-        <v>8000</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40">
         <f t="shared" si="0"/>
-        <v>1.6345723598757272E-3</v>
+        <v>5.4315290673835337E-3</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
-        <v>8500</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.35">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>1.9379453743239433E-3</v>
+        <v>6.4210050770837218E-3</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.35">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42">
         <f t="shared" si="0"/>
-        <v>2.2760878809044566E-3</v>
+        <v>7.5170782388275237E-3</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
-        <v>9500</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.35">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43">
         <f t="shared" si="0"/>
-        <v>2.6506757486755017E-3</v>
+        <v>8.7229420039149769E-3</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44">
         <f t="shared" si="0"/>
-        <v>3.0633294620639323E-3</v>
+        <v>1.0041234530816401E-2</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>10500</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.35">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>3.5156086762653666E-3</v>
+        <v>1.1473997386527171E-2</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.35">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46">
         <f t="shared" si="0"/>
-        <v>4.0090066328439117E-3</v>
+        <v>1.3022636654488842E-2</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.35">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47">
         <f t="shared" si="0"/>
-        <v>4.5449444623392177E-3</v>
+        <v>1.4687887176925568E-2</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48">
         <f t="shared" si="0"/>
-        <v>5.1247654027590517E-3</v>
+        <v>1.6469780667991457E-2</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.35">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49">
         <f t="shared" si="0"/>
-        <v>5.7497289648605621E-3</v>
+        <v>1.8367618430465693E-2</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.35">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50">
         <f t="shared" si="0"/>
-        <v>6.4210050770837218E-3</v>
+        <v>2.0379949391649221E-2</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
-        <v>13500</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.35">
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>7.139668244867739E-3</v>
+        <v>2.2504554142594765E-2</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
-        <v>14000</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52">
         <f t="shared" si="0"/>
-        <v>7.9066917608325293E-3</v>
+        <v>2.4738435618083782E-2</v>
       </c>
       <c r="C52">
         <f t="shared" si="1"/>
-        <v>14500</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.35">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53">
         <f t="shared" si="0"/>
-        <v>8.7229420039149769E-3</v>
+        <v>2.7077816992397724E-2</v>
       </c>
       <c r="C53">
         <f t="shared" si="1"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.35">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>9.5891728669876136E-3</v>
+        <v>2.951814728782165E-2</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
-        <v>15500</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.35">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55">
         <f t="shared" si="0"/>
-        <v>1.0506020353728399E-2</v>
+        <v>3.2054115099261718E-2</v>
       </c>
       <c r="C55">
         <f t="shared" si="1"/>
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>1.1473997386527171E-2</v>
+        <v>3.467967073008181E-2</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
-        <v>16500</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.35">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57">
         <f t="shared" si="0"/>
-        <v>1.2493488867981531E-2</v>
+        <v>3.7388056912446274E-2</v>
       </c>
       <c r="C57">
         <f t="shared" si="1"/>
-        <v>17000</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.35">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58">
         <f t="shared" si="0"/>
-        <v>1.3564747039025687E-2</v>
+        <v>4.0171848151733677E-2</v>
       </c>
       <c r="C58">
         <f t="shared" si="1"/>
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.35">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59">
         <f t="shared" si="0"/>
-        <v>1.4687887176925568E-2</v>
+        <v>4.3022998591062303E-2</v>
       </c>
       <c r="C59">
         <f t="shared" si="1"/>
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60">
         <f t="shared" si="0"/>
-        <v>1.5862883676240225E-2</v>
+        <v>4.5932898141179429E-2</v>
       </c>
       <c r="C60">
         <f t="shared" si="1"/>
-        <v>18500</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.35">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61">
         <f t="shared" si="0"/>
-        <v>1.7089566555369529E-2</v>
+        <v>4.8892436465861083E-2</v>
       </c>
       <c r="C61">
         <f t="shared" si="1"/>
-        <v>19000</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.35">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62">
         <f t="shared" si="0"/>
-        <v>1.8367618430465693E-2</v>
+        <v>5.1892074256846804E-2</v>
       </c>
       <c r="C62">
         <f t="shared" si="1"/>
-        <v>19500</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.35">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63">
         <f t="shared" si="0"/>
-        <v>1.9696571997260381E-2</v>
+        <v>5.4921921078778663E-2</v>
       </c>
       <c r="C63">
         <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>2.1075808059742129E-2</v>
+        <v>5.7971818917411488E-2</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
-        <v>20500</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.35">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>2.2504554142594765E-2</v>
+        <v>6.1031430427395852E-2</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.35">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66">
         <f t="shared" si="0"/>
-        <v>2.3981883721876138E-2</v>
+        <v>6.4090330753079128E-2</v>
       </c>
       <c r="C66">
         <f t="shared" si="1"/>
-        <v>21500</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.35">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>2.5506716105570884E-2</v>
+        <v>6.7138101690766061E-2</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68">
         <f t="shared" si="0"/>
-        <v>2.7077816992397724E-2</v>
+        <v>7.0164426877205852E-2</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
-        <v>22500</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.35">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69">
         <f t="shared" si="0"/>
-        <v>2.8693799733595995E-2</v>
+        <v>7.3159186629829842E-2</v>
       </c>
       <c r="C69">
         <f t="shared" si="1"/>
-        <v>23000</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.35">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70">
         <f t="shared" si="0"/>
-        <v>3.035312731837099E-2</v>
+        <v>7.6112551032035736E-2</v>
       </c>
       <c r="C70">
         <f t="shared" si="1"/>
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.35">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71">
         <f t="shared" si="0"/>
-        <v>3.2054115099261718E-2</v>
+        <v>7.9015069853569708E-2</v>
       </c>
       <c r="C71">
         <f t="shared" si="1"/>
-        <v>24000</v>
-      </c>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72">
         <f t="shared" si="0"/>
-        <v>3.3794934268928725E-2</v>
+        <v>8.1857757923041286E-2</v>
       </c>
       <c r="C72">
         <f t="shared" si="1"/>
-        <v>24500</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.35">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73">
         <f t="shared" si="0"/>
-        <v>3.5573616094775717E-2</v>
+        <v>8.4632174627258694E-2</v>
       </c>
       <c r="C73">
         <f t="shared" si="1"/>
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.35">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74">
         <f t="shared" si="0"/>
-        <v>3.7388056912446274E-2</v>
+        <v>8.7330496299984461E-2</v>
       </c>
       <c r="C74">
         <f t="shared" si="1"/>
-        <v>25500</v>
-      </c>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.35">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75">
         <f t="shared" si="0"/>
-        <v>3.9236023873619186E-2</v>
+        <v>8.9945580379575493E-2</v>
       </c>
       <c r="C75">
         <f t="shared" si="1"/>
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76">
         <f t="shared" si="0"/>
-        <v>4.1115161437703815E-2</v>
+        <v>9.2471020358609296E-2</v>
       </c>
       <c r="C76">
         <f t="shared" si="1"/>
-        <v>26500</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.35">
+        <v>13.25</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77">
         <f t="shared" si="0"/>
-        <v>4.3022998591062303E-2</v>
+        <v>9.4901190715968961E-2</v>
       </c>
       <c r="C77">
         <f t="shared" si="1"/>
-        <v>27000</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.35">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78">
         <f t="shared" si="0"/>
-        <v>4.495695677130844E-2</v>
+        <v>9.7231281209145953E-2</v>
       </c>
       <c r="C78">
         <f t="shared" si="1"/>
-        <v>27500</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.35">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79">
         <f t="shared" si="0"/>
-        <v>4.6914358468115175E-2</v>
+        <v>9.9457320107219804E-2</v>
       </c>
       <c r="C79">
         <f t="shared" si="1"/>
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80">
         <f t="shared" si="0"/>
-        <v>4.8892436465861083E-2</v>
+        <v>0.10157618615802415</v>
       </c>
       <c r="C80">
         <f t="shared" si="1"/>
-        <v>28500</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B81">
         <f t="shared" si="0"/>
-        <v>5.0888343687428006E-2</v>
+        <v>0.1035856093009499</v>
       </c>
       <c r="C81">
         <f t="shared" si="1"/>
-        <v>29000</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B82">
         <f t="shared" si="0"/>
-        <v>5.2899163592589921E-2</v>
+        <v>0.10548416035397182</v>
       </c>
       <c r="C82">
         <f t="shared" si="1"/>
-        <v>29500</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B83">
         <f t="shared" si="0"/>
-        <v>5.4921921078778663E-2</v>
+        <v>0.10727123011408218</v>
       </c>
       <c r="C83">
         <f t="shared" si="1"/>
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B84">
         <f t="shared" si="0"/>
-        <v>5.6953593826638713E-2</v>
+        <v>0.10894699850878881</v>
       </c>
       <c r="C84">
         <f t="shared" si="1"/>
-        <v>30500</v>
-      </c>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.35">
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B85">
         <f t="shared" si="0"/>
-        <v>5.8991124027762909E-2</v>
+        <v>0.11051239461744319</v>
       </c>
       <c r="C85">
         <f t="shared" si="1"/>
-        <v>31000</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.35">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B86">
         <f t="shared" si="0"/>
-        <v>6.1031430427395852E-2</v>
+        <v>0.11196904854019522</v>
       </c>
       <c r="C86">
         <f t="shared" si="1"/>
-        <v>31500</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.35">
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87">
         <f t="shared" si="0"/>
-        <v>6.3071420610770493E-2</v>
+        <v>0.11331923622529684</v>
       </c>
       <c r="C87">
         <f t="shared" si="1"/>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B88">
         <f t="shared" ref="B88:B124" si="2">(1-EXP(-((C88/$B$19-($B$18-0.5))/$B$16)^$B$17))*$B$15</f>
-        <v>6.5108003458162492E-2</v>
+        <v>0.11456581846910648</v>
       </c>
       <c r="C88">
         <f t="shared" si="1"/>
-        <v>32500</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.35">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89">
         <f t="shared" si="2"/>
-        <v>6.7138101690766061E-2</v>
+        <v>0.11571217537522674</v>
       </c>
       <c r="C89">
-        <f t="shared" si="1"/>
-        <v>33000</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.35">
+        <f t="shared" ref="C89:C124" si="3">C88+0.25</f>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90">
         <f t="shared" si="2"/>
-        <v>6.915866442716484E-2</v>
+        <v>0.11676213759849677</v>
       </c>
       <c r="C90">
-        <f t="shared" si="1"/>
-        <v>33500</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B91">
         <f t="shared" si="2"/>
-        <v>7.1166679668536584E-2</v>
+        <v>0.11771991570586685</v>
       </c>
       <c r="C91">
-        <f t="shared" ref="C91:C124" si="3">C90+500</f>
-        <v>34000</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B92">
         <f t="shared" si="2"/>
-        <v>7.3159186629829842E-2</v>
+        <v>0.11859002896034841</v>
       </c>
       <c r="C92">
         <f t="shared" si="3"/>
-        <v>34500</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.35">
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B93">
         <f t="shared" si="2"/>
-        <v>7.5133287834015461E-2</v>
+        <v>0.11937723477809242</v>
       </c>
       <c r="C93">
         <f t="shared" si="3"/>
-        <v>35000</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.35">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B94">
         <f t="shared" si="2"/>
-        <v>7.7086160887166397E-2</v>
+        <v>0.12008646002494117</v>
       </c>
       <c r="C94">
         <f t="shared" si="3"/>
-        <v>35500</v>
-      </c>
-    </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.35">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B95">
         <f t="shared" si="2"/>
-        <v>7.9015069853569708E-2</v>
+        <v>0.12072273521104175</v>
       </c>
       <c r="C95">
         <f t="shared" si="3"/>
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B96">
         <f t="shared" si="2"/>
-        <v>8.0917376152326803E-2</v>
+        <v>0.12129113251445571</v>
       </c>
       <c r="C96">
         <f t="shared" si="3"/>
-        <v>36500</v>
-      </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.35">
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97">
         <f t="shared" si="2"/>
-        <v>8.2790548899946304E-2</v>
+        <v>0.12179670842176366</v>
       </c>
       <c r="C97">
         <f t="shared" si="3"/>
-        <v>37000</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.35">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B98">
         <f t="shared" si="2"/>
-        <v>8.4632174627258694E-2</v>
+        <v>0.12224445162033554</v>
       </c>
       <c r="C98">
         <f t="shared" si="3"/>
-        <v>37500</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.35">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B99">
         <f t="shared" si="2"/>
-        <v>8.643996630355924E-2</v>
+        <v>0.12263923661819812</v>
       </c>
       <c r="C99">
         <f t="shared" si="3"/>
-        <v>38000</v>
-      </c>
-    </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100">
         <f t="shared" si="2"/>
-        <v>8.8211771606171191E-2</v>
+        <v>0.12298578340816241</v>
       </c>
       <c r="C100">
         <f t="shared" si="3"/>
-        <v>38500</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.35">
+        <v>19.25</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101">
         <f t="shared" si="2"/>
-        <v>8.9945580379575493E-2</v>
+        <v>0.12328862333768843</v>
       </c>
       <c r="C101">
         <f t="shared" si="3"/>
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.35">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102">
         <f t="shared" si="2"/>
-        <v>9.1639531234810279E-2</v>
+        <v>0.12355207119904957</v>
       </c>
       <c r="C102">
         <f t="shared" si="3"/>
-        <v>39500</v>
-      </c>
-    </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.35">
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103">
         <f t="shared" si="2"/>
-        <v>9.32919172469414E-2</v>
+        <v>0.12378020341934777</v>
       </c>
       <c r="C103">
         <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104">
         <f t="shared" si="2"/>
-        <v>9.4901190715968961E-2</v>
+        <v>0.1239768421098045</v>
       </c>
       <c r="C104">
         <f t="shared" si="3"/>
-        <v>40500</v>
-      </c>
-    </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.35">
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105">
         <f t="shared" si="2"/>
-        <v>9.6465966964479927E-2</v>
+        <v>0.12414554463077215</v>
       </c>
       <c r="C105">
         <f t="shared" si="3"/>
-        <v>41000</v>
-      </c>
-    </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.35">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106">
         <f t="shared" si="2"/>
-        <v>9.7985027153597692E-2</v>
+        <v>0.12428959824458628</v>
       </c>
       <c r="C106">
         <f t="shared" si="3"/>
-        <v>41500</v>
-      </c>
-    </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.35">
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B107">
         <f t="shared" si="2"/>
-        <v>9.9457320107219804E-2</v>
+        <v>0.12441201936347031</v>
       </c>
       <c r="C107">
         <f t="shared" si="3"/>
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108">
         <f t="shared" si="2"/>
-        <v>0.10088196314308123</v>
+        <v>0.12451555685425303</v>
       </c>
       <c r="C108">
         <f t="shared" si="3"/>
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.35">
+        <v>21.25</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109">
         <f t="shared" si="2"/>
-        <v>0.10225824191772932</v>
+        <v>0.12460269883504811</v>
       </c>
       <c r="C109">
         <f t="shared" si="3"/>
-        <v>43000</v>
-      </c>
-    </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.35">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B110">
         <f t="shared" si="2"/>
-        <v>0.1035856093009499</v>
+        <v>0.12467568239008178</v>
       </c>
       <c r="C110">
         <f t="shared" si="3"/>
-        <v>43500</v>
-      </c>
-    </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.35">
+        <v>21.75</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B111">
         <f t="shared" si="2"/>
-        <v>0.10486368330344273</v>
+        <v>0.12473650563587114</v>
       </c>
       <c r="C111">
         <f t="shared" si="3"/>
-        <v>44000</v>
-      </c>
-    </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B112">
         <f t="shared" si="2"/>
-        <v>0.10609224408950788</v>
+        <v>0.12478694159291652</v>
       </c>
       <c r="C112">
         <f t="shared" si="3"/>
-        <v>44500</v>
-      </c>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.35">
+        <v>22.25</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B113">
         <f t="shared" si="2"/>
-        <v>0.10727123011408218</v>
+        <v>0.12482855334969299</v>
       </c>
       <c r="C113">
         <f t="shared" si="3"/>
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.35">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B114">
         <f t="shared" si="2"/>
-        <v>0.10840073343056618</v>
+        <v>0.12486271004758752</v>
       </c>
       <c r="C114">
         <f t="shared" si="3"/>
-        <v>45500</v>
-      </c>
-    </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.35">
+        <v>22.75</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B115">
         <f t="shared" si="2"/>
-        <v>0.10948099422242338</v>
+        <v>0.12489060326408261</v>
       </c>
       <c r="C115">
         <f t="shared" si="3"/>
-        <v>46000</v>
-      </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B116">
         <f t="shared" si="2"/>
-        <v>0.11051239461744319</v>
+        <v>0.12491326342455751</v>
       </c>
       <c r="C116">
         <f t="shared" si="3"/>
-        <v>46500</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.35">
+        <v>23.25</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B117">
         <f t="shared" si="2"/>
-        <v>0.11149545184876868</v>
+        <v>0.12493157592833935</v>
       </c>
       <c r="C117">
         <f t="shared" si="3"/>
-        <v>47000</v>
-      </c>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.35">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B118">
         <f t="shared" si="2"/>
-        <v>0.11243081083124459</v>
+        <v>0.12494629673008874</v>
       </c>
       <c r="C118">
         <f t="shared" si="3"/>
-        <v>47500</v>
-      </c>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.35">
+        <v>23.75</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B119">
         <f t="shared" si="2"/>
-        <v>0.11331923622529684</v>
+        <v>0.12495806717151219</v>
       </c>
       <c r="C119">
         <f t="shared" si="3"/>
-        <v>48000</v>
-      </c>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B120">
         <f t="shared" si="2"/>
-        <v>0.11416160406337549</v>
+        <v>0.12496742790932699</v>
       </c>
       <c r="C120">
         <f t="shared" si="3"/>
-        <v>48500</v>
-      </c>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.35">
+        <v>24.25</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B121">
         <f t="shared" si="2"/>
-        <v>0.11495889301595999</v>
+        <v>0.1249748318322462</v>
       </c>
       <c r="C121">
         <f t="shared" si="3"/>
-        <v>49000</v>
-      </c>
-    </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.35">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B122">
         <f t="shared" si="2"/>
-        <v>0.11571217537522674</v>
+        <v>0.12498065590169766</v>
       </c>
       <c r="C122">
         <f t="shared" si="3"/>
-        <v>49500</v>
-      </c>
-    </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.35">
+        <v>24.75</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B123">
         <f t="shared" si="2"/>
-        <v>0.11642260783471928</v>
+        <v>0.12498521188753921</v>
       </c>
       <c r="C123">
         <f t="shared" si="3"/>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B124">
         <f t="shared" si="2"/>
-        <v>0.11709142214275396</v>
+        <v>0.1249887560009456</v>
       </c>
       <c r="C124">
         <f t="shared" si="3"/>
-        <v>50500</v>
+        <v>25.25</v>
       </c>
     </row>
   </sheetData>
@@ -5405,13 +5406,13 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:CF2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -5741,14 +5742,14 @@
       </c>
       <c r="CE1">
         <f>(1-EXP(-((CE2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.1239768421098045</v>
+        <v>0.125</v>
       </c>
       <c r="CF1">
         <f>(1-EXP(-((CF2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
         <v>0.125</v>
       </c>
     </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -5756,331 +5757,330 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <f>B2+750</f>
-        <v>750</v>
+        <f>B2+0.25</f>
+        <v>0.25</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:BO2" si="0">C2+750</f>
-        <v>1500</v>
+        <f t="shared" ref="D2:AI2" si="0">C2+0.25</f>
+        <v>0.5</v>
       </c>
       <c r="E2">
         <f t="shared" si="0"/>
-        <v>2250</v>
+        <v>0.75</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>3000</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>3750</v>
+        <v>1.25</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>4500</v>
+        <v>1.5</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>5250</v>
+        <v>1.75</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>2</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>6750</v>
+        <v>2.25</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>7500</v>
+        <v>2.5</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>8250</v>
+        <v>2.75</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>9000</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>9750</v>
+        <v>3.25</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>10500</v>
+        <v>3.5</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>11250</v>
+        <v>3.75</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>12000</v>
+        <v>4</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>12750</v>
+        <v>4.25</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>13500</v>
+        <v>4.5</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>14250</v>
+        <v>4.75</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>15000</v>
+        <v>5</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>15750</v>
+        <v>5.25</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>16500</v>
+        <v>5.5</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>17250</v>
+        <v>5.75</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>18000</v>
+        <v>6</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>18750</v>
+        <v>6.25</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>19500</v>
+        <v>6.5</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>20250</v>
+        <v>6.75</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>21000</v>
+        <v>7</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>21750</v>
+        <v>7.25</v>
       </c>
       <c r="AF2">
         <f t="shared" si="0"/>
-        <v>22500</v>
+        <v>7.5</v>
       </c>
       <c r="AG2">
         <f t="shared" si="0"/>
-        <v>23250</v>
+        <v>7.75</v>
       </c>
       <c r="AH2">
         <f t="shared" si="0"/>
-        <v>24000</v>
+        <v>8</v>
       </c>
       <c r="AI2">
         <f t="shared" si="0"/>
-        <v>24750</v>
+        <v>8.25</v>
       </c>
       <c r="AJ2">
-        <f t="shared" si="0"/>
-        <v>25500</v>
+        <f>AI2+0.25</f>
+        <v>8.5</v>
       </c>
       <c r="AK2">
-        <f t="shared" si="0"/>
-        <v>26250</v>
+        <f t="shared" ref="AK2:AO2" si="1">AJ2+0.25</f>
+        <v>8.75</v>
       </c>
       <c r="AL2">
-        <f t="shared" si="0"/>
-        <v>27000</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="AM2">
-        <f t="shared" si="0"/>
-        <v>27750</v>
+        <f t="shared" si="1"/>
+        <v>9.25</v>
       </c>
       <c r="AN2">
-        <f t="shared" si="0"/>
-        <v>28500</v>
+        <f t="shared" si="1"/>
+        <v>9.5</v>
       </c>
       <c r="AO2">
-        <f t="shared" si="0"/>
-        <v>29250</v>
+        <f t="shared" si="1"/>
+        <v>9.75</v>
       </c>
       <c r="AP2">
-        <f t="shared" si="0"/>
-        <v>30000</v>
+        <f>AO2+0.25</f>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <f t="shared" si="0"/>
-        <v>30750</v>
+        <f t="shared" ref="AQ2:BJ2" si="2">AP2+0.25</f>
+        <v>10.25</v>
       </c>
       <c r="AR2">
-        <f t="shared" si="0"/>
-        <v>31500</v>
+        <f t="shared" si="2"/>
+        <v>10.5</v>
       </c>
       <c r="AS2">
-        <f t="shared" si="0"/>
-        <v>32250</v>
+        <f t="shared" si="2"/>
+        <v>10.75</v>
       </c>
       <c r="AT2">
-        <f t="shared" si="0"/>
-        <v>33000</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="AU2">
-        <f t="shared" si="0"/>
-        <v>33750</v>
+        <f t="shared" si="2"/>
+        <v>11.25</v>
       </c>
       <c r="AV2">
-        <f t="shared" si="0"/>
-        <v>34500</v>
+        <f t="shared" si="2"/>
+        <v>11.5</v>
       </c>
       <c r="AW2">
-        <f t="shared" si="0"/>
-        <v>35250</v>
+        <f t="shared" si="2"/>
+        <v>11.75</v>
       </c>
       <c r="AX2">
-        <f t="shared" si="0"/>
-        <v>36000</v>
+        <f t="shared" si="2"/>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <f t="shared" si="0"/>
-        <v>36750</v>
+        <f t="shared" si="2"/>
+        <v>12.25</v>
       </c>
       <c r="AZ2">
-        <f t="shared" si="0"/>
-        <v>37500</v>
+        <f t="shared" si="2"/>
+        <v>12.5</v>
       </c>
       <c r="BA2">
-        <f t="shared" si="0"/>
-        <v>38250</v>
+        <f t="shared" si="2"/>
+        <v>12.75</v>
       </c>
       <c r="BB2">
-        <f t="shared" si="0"/>
-        <v>39000</v>
+        <f t="shared" si="2"/>
+        <v>13</v>
       </c>
       <c r="BC2">
-        <f t="shared" si="0"/>
-        <v>39750</v>
+        <f t="shared" si="2"/>
+        <v>13.25</v>
       </c>
       <c r="BD2">
-        <f t="shared" si="0"/>
-        <v>40500</v>
+        <f t="shared" si="2"/>
+        <v>13.5</v>
       </c>
       <c r="BE2">
-        <f t="shared" si="0"/>
-        <v>41250</v>
+        <f t="shared" si="2"/>
+        <v>13.75</v>
       </c>
       <c r="BF2">
-        <f t="shared" si="0"/>
-        <v>42000</v>
+        <f t="shared" si="2"/>
+        <v>14</v>
       </c>
       <c r="BG2">
-        <f t="shared" si="0"/>
-        <v>42750</v>
+        <f t="shared" si="2"/>
+        <v>14.25</v>
       </c>
       <c r="BH2">
-        <f t="shared" si="0"/>
-        <v>43500</v>
+        <f t="shared" si="2"/>
+        <v>14.5</v>
       </c>
       <c r="BI2">
-        <f t="shared" si="0"/>
-        <v>44250</v>
+        <f t="shared" si="2"/>
+        <v>14.75</v>
       </c>
       <c r="BJ2">
-        <f t="shared" si="0"/>
-        <v>45000</v>
+        <f t="shared" si="2"/>
+        <v>15</v>
       </c>
       <c r="BK2">
-        <f t="shared" si="0"/>
-        <v>45750</v>
+        <f t="shared" ref="BK2" si="3">BJ2+0.25</f>
+        <v>15.25</v>
       </c>
       <c r="BL2">
-        <f t="shared" si="0"/>
-        <v>46500</v>
+        <f t="shared" ref="BL2" si="4">BK2+0.25</f>
+        <v>15.5</v>
       </c>
       <c r="BM2">
-        <f t="shared" si="0"/>
-        <v>47250</v>
+        <f t="shared" ref="BM2" si="5">BL2+0.25</f>
+        <v>15.75</v>
       </c>
       <c r="BN2">
-        <f t="shared" si="0"/>
-        <v>48000</v>
+        <f t="shared" ref="BN2" si="6">BM2+0.25</f>
+        <v>16</v>
       </c>
       <c r="BO2">
-        <f t="shared" si="0"/>
-        <v>48750</v>
+        <f t="shared" ref="BO2" si="7">BN2+0.25</f>
+        <v>16.25</v>
       </c>
       <c r="BP2">
-        <f t="shared" ref="BP2:CE2" si="1">BO2+750</f>
-        <v>49500</v>
+        <f t="shared" ref="BP2" si="8">BO2+0.25</f>
+        <v>16.5</v>
       </c>
       <c r="BQ2">
-        <f t="shared" si="1"/>
-        <v>50250</v>
+        <f t="shared" ref="BQ2" si="9">BP2+0.25</f>
+        <v>16.75</v>
       </c>
       <c r="BR2">
-        <f t="shared" si="1"/>
-        <v>51000</v>
+        <f t="shared" ref="BR2" si="10">BQ2+0.25</f>
+        <v>17</v>
       </c>
       <c r="BS2">
-        <f t="shared" si="1"/>
-        <v>51750</v>
+        <f t="shared" ref="BS2" si="11">BR2+0.25</f>
+        <v>17.25</v>
       </c>
       <c r="BT2">
-        <f t="shared" si="1"/>
-        <v>52500</v>
+        <f t="shared" ref="BT2" si="12">BS2+0.25</f>
+        <v>17.5</v>
       </c>
       <c r="BU2">
-        <f t="shared" si="1"/>
-        <v>53250</v>
+        <f t="shared" ref="BU2" si="13">BT2+0.25</f>
+        <v>17.75</v>
       </c>
       <c r="BV2">
-        <f t="shared" si="1"/>
-        <v>54000</v>
+        <f t="shared" ref="BV2" si="14">BU2+0.25</f>
+        <v>18</v>
       </c>
       <c r="BW2">
-        <f t="shared" si="1"/>
-        <v>54750</v>
+        <f t="shared" ref="BW2" si="15">BV2+0.25</f>
+        <v>18.25</v>
       </c>
       <c r="BX2">
-        <f t="shared" si="1"/>
-        <v>55500</v>
+        <f t="shared" ref="BX2" si="16">BW2+0.25</f>
+        <v>18.5</v>
       </c>
       <c r="BY2">
-        <f t="shared" si="1"/>
-        <v>56250</v>
+        <f t="shared" ref="BY2" si="17">BX2+0.25</f>
+        <v>18.75</v>
       </c>
       <c r="BZ2">
-        <f t="shared" si="1"/>
-        <v>57000</v>
+        <f t="shared" ref="BZ2" si="18">BY2+0.25</f>
+        <v>19</v>
       </c>
       <c r="CA2">
-        <f t="shared" si="1"/>
-        <v>57750</v>
+        <f t="shared" ref="CA2" si="19">BZ2+0.25</f>
+        <v>19.25</v>
       </c>
       <c r="CB2">
-        <f t="shared" si="1"/>
-        <v>58500</v>
+        <f t="shared" ref="CB2" si="20">CA2+0.25</f>
+        <v>19.5</v>
       </c>
       <c r="CC2">
-        <f t="shared" si="1"/>
-        <v>59250</v>
+        <f t="shared" ref="CC2" si="21">CB2+0.25</f>
+        <v>19.75</v>
       </c>
       <c r="CD2">
-        <f t="shared" si="1"/>
-        <v>60000</v>
+        <f t="shared" ref="CD2" si="22">CC2+0.25</f>
+        <v>20</v>
       </c>
       <c r="CE2">
-        <f t="shared" si="1"/>
-        <v>60750</v>
-      </c>
-      <c r="CF2" s="2">
-        <v>1000000</v>
+        <v>1000</v>
+      </c>
+      <c r="CF2">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
@@ -6095,17 +6095,17 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -6124,12 +6124,12 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -6699,7 +6699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -7459,7 +7459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -7649,7 +7649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -8409,7 +8409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>28</v>
       </c>

--- a/InputData/elec/CSC/Capacity Supply Curve.xlsx
+++ b/InputData/elec/CSC/Capacity Supply Curve.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\CSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6367CB4D-9140-4286-9A37-2062052CD2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9418ED56-1826-4582-AB9F-4771E1D027D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{F87DB1D1-DC21-4EA7-B1DF-998EE56837F8}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -214,9 +214,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -306,307 +307,307 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>0.25</c:v>
+                  <c:v>500</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.75</c:v>
+                  <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>2000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.25</c:v>
+                  <c:v>2500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.75</c:v>
+                  <c:v>3500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>4000</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.25</c:v>
+                  <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.5</c:v>
+                  <c:v>5000</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.75</c:v>
+                  <c:v>5500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.25</c:v>
+                  <c:v>6500</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.5</c:v>
+                  <c:v>7000</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.75</c:v>
+                  <c:v>7500</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4</c:v>
+                  <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.25</c:v>
+                  <c:v>8500</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.5</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.75</c:v>
+                  <c:v>9500</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>5</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5.25</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.5</c:v>
+                  <c:v>11000</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.75</c:v>
+                  <c:v>11500</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>6</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6.25</c:v>
+                  <c:v>12500</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.5</c:v>
+                  <c:v>13000</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.75</c:v>
+                  <c:v>13500</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>7</c:v>
+                  <c:v>14000</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7.25</c:v>
+                  <c:v>14500</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7.5</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.75</c:v>
+                  <c:v>15500</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>8</c:v>
+                  <c:v>16000</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8.25</c:v>
+                  <c:v>16500</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.5</c:v>
+                  <c:v>17000</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>8.75</c:v>
+                  <c:v>17500</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>9</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>9.25</c:v>
+                  <c:v>18500</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>9.5</c:v>
+                  <c:v>19000</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>9.75</c:v>
+                  <c:v>19500</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>10</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10.25</c:v>
+                  <c:v>20500</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>10.5</c:v>
+                  <c:v>21000</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>10.75</c:v>
+                  <c:v>21500</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>11</c:v>
+                  <c:v>22000</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>11.25</c:v>
+                  <c:v>22500</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>11.5</c:v>
+                  <c:v>23000</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>11.75</c:v>
+                  <c:v>23500</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>12</c:v>
+                  <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>12.25</c:v>
+                  <c:v>24500</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>12.5</c:v>
+                  <c:v>25000</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>12.75</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>13</c:v>
+                  <c:v>26000</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>13.25</c:v>
+                  <c:v>26500</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>13.5</c:v>
+                  <c:v>27000</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>13.75</c:v>
+                  <c:v>27500</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>14</c:v>
+                  <c:v>28000</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>14.25</c:v>
+                  <c:v>28500</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>14.5</c:v>
+                  <c:v>29000</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>14.75</c:v>
+                  <c:v>29500</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>15</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>15.25</c:v>
+                  <c:v>30500</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>15.5</c:v>
+                  <c:v>31000</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>15.75</c:v>
+                  <c:v>31500</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>16</c:v>
+                  <c:v>32000</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>16.25</c:v>
+                  <c:v>32500</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>16.5</c:v>
+                  <c:v>33000</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>16.75</c:v>
+                  <c:v>33500</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>17</c:v>
+                  <c:v>34000</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>17.25</c:v>
+                  <c:v>34500</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>17.5</c:v>
+                  <c:v>35000</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>17.75</c:v>
+                  <c:v>35500</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>18</c:v>
+                  <c:v>36000</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>18.25</c:v>
+                  <c:v>36500</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>18.5</c:v>
+                  <c:v>37000</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>18.75</c:v>
+                  <c:v>37500</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>19</c:v>
+                  <c:v>38000</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>19.25</c:v>
+                  <c:v>38500</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>19.5</c:v>
+                  <c:v>39000</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>19.75</c:v>
+                  <c:v>39500</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>20</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>20.25</c:v>
+                  <c:v>40500</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>20.5</c:v>
+                  <c:v>41000</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>20.75</c:v>
+                  <c:v>41500</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>21</c:v>
+                  <c:v>42000</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>21.25</c:v>
+                  <c:v>42500</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>21.5</c:v>
+                  <c:v>43000</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>21.75</c:v>
+                  <c:v>43500</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>22</c:v>
+                  <c:v>44000</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>22.25</c:v>
+                  <c:v>44500</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>22.5</c:v>
+                  <c:v>45000</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>22.75</c:v>
+                  <c:v>45500</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>23</c:v>
+                  <c:v>46000</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>23.25</c:v>
+                  <c:v>46500</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>23.5</c:v>
+                  <c:v>47000</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>23.75</c:v>
+                  <c:v>47500</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>24</c:v>
+                  <c:v>48000</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>24.25</c:v>
+                  <c:v>48500</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>24.5</c:v>
+                  <c:v>49000</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>24.75</c:v>
+                  <c:v>49500</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>25</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>25.25</c:v>
+                  <c:v>50500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -618,307 +619,307 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>1.1302755611730664E-6</c:v>
+                  <c:v>4.688565392790833E-7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.041918329455445E-6</c:v>
+                  <c:v>3.7508171421674062E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.0513853137847935E-5</c:v>
+                  <c:v>1.2658685661237622E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.2317035876470759E-5</c:v>
+                  <c:v>3.0004286253101917E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4120526808655831E-4</c:v>
+                  <c:v>5.8597333307211504E-5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.4390236156555944E-4</c:v>
+                  <c:v>1.0124385022705905E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.8708568873771498E-4</c:v>
+                  <c:v>1.607441383691538E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.7736617667798751E-4</c:v>
+                  <c:v>2.3989029825592642E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>8.2126483012147367E-4</c:v>
+                  <c:v>3.4146330619178321E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.1251859013301779E-3</c:v>
+                  <c:v>4.6822965062173478E-4</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.4953868620252581E-3</c:v>
+                  <c:v>6.229375339770665E-4</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.9379453743239433E-3</c:v>
+                  <c:v>8.0831264734918245E-4</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.4587235032284965E-3</c:v>
+                  <c:v>1.0270535271122315E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.0633294620639323E-3</c:v>
+                  <c:v>1.2818265045742155E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.7570772335819985E-3</c:v>
+                  <c:v>1.5752602618622491E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.5449444623392177E-3</c:v>
+                  <c:v>1.9099400095324429E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.4315290673835337E-3</c:v>
+                  <c:v>2.288401303826018E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>6.4210050770837218E-3</c:v>
+                  <c:v>2.7131235240535206E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>7.5170782388275237E-3</c:v>
+                  <c:v>3.1865230332662389E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.7229420039149769E-3</c:v>
+                  <c:v>3.710946048145702E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.0041234530816401E-2</c:v>
+                  <c:v>4.2886612468895045E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.1473997386527171E-2</c:v>
+                  <c:v>4.9218521467715125E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.3022636654488842E-2</c:v>
+                  <c:v>5.6126092859814757E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.4687887176925568E-2</c:v>
+                  <c:v>6.3629222472749046E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.6469780667991457E-2</c:v>
+                  <c:v>7.1746715638626715E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.8367618430465693E-2</c:v>
+                  <c:v>8.0496205508047858E-3</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>2.0379949391649221E-2</c:v>
+                  <c:v>8.9894071079172095E-3</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.2504554142594765E-2</c:v>
+                  <c:v>9.9955355428148346E-3</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.4738435618083782E-2</c:v>
+                  <c:v>1.1069368465165541E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.7077816992397724E-2</c:v>
+                  <c:v>1.2212118805480968E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.951814728782165E-2</c:v>
+                  <c:v>1.3424842013782658E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>3.2054115099261718E-2</c:v>
+                  <c:v>1.4708428495219757E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>3.467967073008181E-2</c:v>
+                  <c:v>1.6063596341138037E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>3.7388056912446274E-2</c:v>
+                  <c:v>1.7490884415174143E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4.0171848151733677E-2</c:v>
+                  <c:v>1.899064585463596E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.3022998591062303E-2</c:v>
+                  <c:v>2.0563042047695795E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.5932898141179429E-2</c:v>
+                  <c:v>2.2208037146736314E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4.8892436465861083E-2</c:v>
+                  <c:v>2.3925393177517337E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>5.1892074256846804E-2</c:v>
+                  <c:v>2.571466580265197E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5.4921921078778663E-2</c:v>
+                  <c:v>2.7575200796164531E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5.7971818917411488E-2</c:v>
+                  <c:v>2.9506131283638978E-2</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>6.1031430427395852E-2</c:v>
+                  <c:v>3.1506375799632669E-2</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>6.4090330753079128E-2</c:v>
+                  <c:v>3.357463721062659E-2</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>6.7138101690766061E-2</c:v>
+                  <c:v>3.5709402547799238E-2</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>7.0164426877205852E-2</c:v>
+                  <c:v>3.790894378935681E-2</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>7.3159186629829842E-2</c:v>
+                  <c:v>4.0171319627034394E-2</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>7.6112551032035736E-2</c:v>
+                  <c:v>4.2494378245719382E-2</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>7.9015069853569708E-2</c:v>
+                  <c:v>4.4875761138966401E-2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>8.1857757923041286E-2</c:v>
+                  <c:v>4.7312907976500215E-2</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>8.4632174627258694E-2</c:v>
+                  <c:v>4.9803062532686002E-2</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>8.7330496299984461E-2</c:v>
+                  <c:v>5.2343279677424782E-2</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>8.9945580379575493E-2</c:v>
+                  <c:v>5.4930433423066853E-2</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>9.2471020358609296E-2</c:v>
+                  <c:v>5.7561226012785335E-2</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>9.4901190715968961E-2</c:v>
+                  <c:v>6.0232198027487222E-2</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>9.7231281209145953E-2</c:v>
+                  <c:v>6.2939739479831808E-2</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>9.9457320107219804E-2</c:v>
+                  <c:v>6.5680101855361245E-2</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.10157618615802415</c:v>
+                  <c:v>6.8449411052205505E-2</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1035856093009499</c:v>
+                  <c:v>7.1243681162399208E-2</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.10548416035397182</c:v>
+                  <c:v>7.4058829029625878E-2</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.10727123011408218</c:v>
+                  <c:v>7.6890689510290128E-2</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.10894699850878881</c:v>
+                  <c:v>7.9735031357294192E-2</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.11051239461744319</c:v>
+                  <c:v>8.2587573638868067E-2</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.11196904854019522</c:v>
+                  <c:v>8.5444002598354191E-2</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.11331923622529684</c:v>
+                  <c:v>8.8299988855078684E-2</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.11456581846910648</c:v>
+                  <c:v>9.1151204841427483E-2</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.11571217537522674</c:v>
+                  <c:v>9.3993342367072477E-2</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.11676213759849677</c:v>
+                  <c:v>9.6822130198030765E-2</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.11771991570586685</c:v>
+                  <c:v>9.9633351535951209E-2</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.11859002896034841</c:v>
+                  <c:v>0.10242286128176177</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.11937723477809242</c:v>
+                  <c:v>0.10518660296762164</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.12008646002494117</c:v>
+                  <c:v>0.10792062524203296</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.12072273521104175</c:v>
+                  <c:v>0.11062109779499758</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.12129113251445571</c:v>
+                  <c:v>0.11328432661325752</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.12179670842176366</c:v>
+                  <c:v>0.11590676845992481</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.12224445162033554</c:v>
+                  <c:v>0.11848504447816216</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.12263923661819812</c:v>
+                  <c:v>0.12101595282498293</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.12298578340816241</c:v>
+                  <c:v>0.12349648024863966</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.12328862333768843</c:v>
+                  <c:v>0.12592381253140569</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.12355207119904957</c:v>
+                  <c:v>0.12829534372873438</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.12378020341934777</c:v>
+                  <c:v>0.13060868414571794</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.1239768421098045</c:v>
+                  <c:v>0.13286166700235655</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.12414554463077215</c:v>
+                  <c:v>0.13505235375027189</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.12428959824458628</c:v>
+                  <c:v>0.13717903801503675</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.12441201936347031</c:v>
+                  <c:v>0.13924024815010771</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.12451555685425303</c:v>
+                  <c:v>0.14123474840031372</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.12460269883504811</c:v>
+                  <c:v>0.14316153868482104</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.12467568239008178</c:v>
+                  <c:v>0.14501985302132986</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.12473650563587114</c:v>
+                  <c:v>0.1468091566248198</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.12478694159291652</c:v>
+                  <c:v>0.14852914172531101</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.12482855334969299</c:v>
+                  <c:v>0.15017972215971503</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.12486271004758752</c:v>
+                  <c:v>0.15176102680279263</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.12489060326408261</c:v>
+                  <c:v>0.15327339191139272</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.12491326342455751</c:v>
+                  <c:v>0.15471735246442045</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.12493157592833935</c:v>
+                  <c:v>0.15609363258827613</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.12494629673008874</c:v>
+                  <c:v>0.15740313516374241</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.12495806717151219</c:v>
+                  <c:v>0.15864693071541558</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.12496742790932699</c:v>
+                  <c:v>0.15982624568872567</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.1249748318322462</c:v>
+                  <c:v>0.16094245022234396</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.12498065590169766</c:v>
+                  <c:v>0.16199704552531743</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.12498521188753921</c:v>
+                  <c:v>0.16299165096860699</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.1249887560009456</c:v>
+                  <c:v>0.16392799099985553</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1075,6 +1076,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1082,7 +1084,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1204,124 +1205,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
+                  <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.75</c:v>
+                  <c:v>2250</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.25</c:v>
+                  <c:v>3750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5</c:v>
+                  <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.75</c:v>
+                  <c:v>5250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.25</c:v>
+                  <c:v>6750</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.5</c:v>
+                  <c:v>7500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.75</c:v>
+                  <c:v>8250</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.25</c:v>
+                  <c:v>9750</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.5</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.75</c:v>
+                  <c:v>11250</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.25</c:v>
+                  <c:v>12750</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.5</c:v>
+                  <c:v>13500</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.75</c:v>
+                  <c:v>14250</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.25</c:v>
+                  <c:v>15750</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.5</c:v>
+                  <c:v>16500</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.75</c:v>
+                  <c:v>17250</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.25</c:v>
+                  <c:v>18750</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.5</c:v>
+                  <c:v>19500</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6.75</c:v>
+                  <c:v>20250</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7</c:v>
+                  <c:v>21000</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7.25</c:v>
+                  <c:v>21750</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.5</c:v>
+                  <c:v>22500</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7.75</c:v>
+                  <c:v>23250</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8</c:v>
+                  <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.25</c:v>
+                  <c:v>24750</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>8.5</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>8.75</c:v>
+                  <c:v>26250</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>9</c:v>
+                  <c:v>27000</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>9.25</c:v>
+                  <c:v>27750</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>9.5</c:v>
+                  <c:v>28500</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>9.75</c:v>
+                  <c:v>29250</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1336,124 +1337,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1302755611730664E-6</c:v>
+                  <c:v>1.5823857856422929E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.041918329455445E-6</c:v>
+                  <c:v>1.2658685661237622E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.0513853137847935E-5</c:v>
+                  <c:v>4.2719394392987109E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.2317035876470759E-5</c:v>
+                  <c:v>1.0124385022705905E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.4120526808655831E-4</c:v>
+                  <c:v>1.9768737532118162E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.4390236156555944E-4</c:v>
+                  <c:v>3.4146330619178321E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.8708568873771498E-4</c:v>
+                  <c:v>5.4191996423280089E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.7736617667798751E-4</c:v>
+                  <c:v>8.0831264734918245E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.2126483012147367E-4</c:v>
+                  <c:v>1.149770762170063E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.1251859013301779E-3</c:v>
+                  <c:v>1.5752602618622491E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.4953868620252581E-3</c:v>
+                  <c:v>2.093541606835361E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.9379453743239433E-3</c:v>
+                  <c:v>2.7131235240535206E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.4587235032284965E-3</c:v>
+                  <c:v>3.4422129045198948E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.0633294620639323E-3</c:v>
+                  <c:v>4.2886612468895045E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.7570772335819985E-3</c:v>
+                  <c:v>5.2599081270147978E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.5449444623392177E-3</c:v>
+                  <c:v>6.3629222472749046E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.4315290673835337E-3</c:v>
+                  <c:v>7.604140694336947E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.4210050770837218E-3</c:v>
+                  <c:v>8.9894071079172095E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.5170782388275237E-3</c:v>
+                  <c:v>1.0523909534358533E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.7229420039149769E-3</c:v>
+                  <c:v>1.2212118805480968E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.0041234530816401E-2</c:v>
+                  <c:v>1.405772834314296E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.1473997386527171E-2</c:v>
+                  <c:v>1.6063596341138037E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.3022636654488842E-2</c:v>
+                  <c:v>1.8231691316284378E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.4687887176925568E-2</c:v>
+                  <c:v>2.0563042047695795E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.6469780667991457E-2</c:v>
+                  <c:v>2.3057692935188039E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.8367618430465693E-2</c:v>
+                  <c:v>2.571466580265197E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.0379949391649221E-2</c:v>
+                  <c:v>2.8531929148308908E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.2504554142594765E-2</c:v>
+                  <c:v>3.1506375799632669E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.4738435618083782E-2</c:v>
+                  <c:v>3.4633809865317292E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.7077816992397724E-2</c:v>
+                  <c:v>3.790894378935681E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.951814728782165E-2</c:v>
+                  <c:v>4.1325406202950304E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>3.2054115099261718E-2</c:v>
+                  <c:v>4.4875761138966401E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>3.467967073008181E-2</c:v>
+                  <c:v>4.855153902211453E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>3.7388056912446274E-2</c:v>
+                  <c:v>5.2343279677424782E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.0171848151733677E-2</c:v>
+                  <c:v>5.6240587412427143E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.3022998591062303E-2</c:v>
+                  <c:v>6.0232198027487222E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4.5932898141179429E-2</c:v>
+                  <c:v>6.4306057397651203E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4.8892436465861083E-2</c:v>
+                  <c:v>6.8449411052205505E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5.1892074256846804E-2</c:v>
+                  <c:v>7.2648903959585523E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5.4921921078778663E-2</c:v>
+                  <c:v>7.6890689510290128E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1610,6 +1611,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1617,7 +1619,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1739,124 +1740,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.25</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.5</c:v>
+                  <c:v>1500</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.75</c:v>
+                  <c:v>2250</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.25</c:v>
+                  <c:v>3750</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5</c:v>
+                  <c:v>4500</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.75</c:v>
+                  <c:v>5250</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2</c:v>
+                  <c:v>6000</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.25</c:v>
+                  <c:v>6750</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.5</c:v>
+                  <c:v>7500</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.75</c:v>
+                  <c:v>8250</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3</c:v>
+                  <c:v>9000</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3.25</c:v>
+                  <c:v>9750</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.5</c:v>
+                  <c:v>10500</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.75</c:v>
+                  <c:v>11250</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4</c:v>
+                  <c:v>12000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>4.25</c:v>
+                  <c:v>12750</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.5</c:v>
+                  <c:v>13500</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.75</c:v>
+                  <c:v>14250</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>5</c:v>
+                  <c:v>15000</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>5.25</c:v>
+                  <c:v>15750</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>5.5</c:v>
+                  <c:v>16500</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>5.75</c:v>
+                  <c:v>17250</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>6</c:v>
+                  <c:v>18000</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>6.25</c:v>
+                  <c:v>18750</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>6.5</c:v>
+                  <c:v>19500</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>6.75</c:v>
+                  <c:v>20250</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>7</c:v>
+                  <c:v>21000</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>7.25</c:v>
+                  <c:v>21750</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>7.5</c:v>
+                  <c:v>22500</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>7.75</c:v>
+                  <c:v>23250</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>8</c:v>
+                  <c:v>24000</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>8.25</c:v>
+                  <c:v>24750</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>8.5</c:v>
+                  <c:v>25500</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>8.75</c:v>
+                  <c:v>26250</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>9</c:v>
+                  <c:v>27000</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>9.25</c:v>
+                  <c:v>27750</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>9.5</c:v>
+                  <c:v>28500</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>9.75</c:v>
+                  <c:v>29250</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1871,124 +1872,124 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1302755611730664E-6</c:v>
+                  <c:v>1.5823857856422929E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.041918329455445E-6</c:v>
+                  <c:v>1.2658685661237622E-5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.0513853137847935E-5</c:v>
+                  <c:v>4.2719394392987109E-5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.2317035876470759E-5</c:v>
+                  <c:v>1.0124385022705905E-4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.4120526808655831E-4</c:v>
+                  <c:v>1.9768737532118162E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.4390236156555944E-4</c:v>
+                  <c:v>3.4146330619178321E-4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.8708568873771498E-4</c:v>
+                  <c:v>5.4191996423280089E-4</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.7736617667798751E-4</c:v>
+                  <c:v>8.0831264734918245E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.2126483012147367E-4</c:v>
+                  <c:v>1.149770762170063E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.1251859013301779E-3</c:v>
+                  <c:v>1.5752602618622491E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.4953868620252581E-3</c:v>
+                  <c:v>2.093541606835361E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.9379453743239433E-3</c:v>
+                  <c:v>2.7131235240535206E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.4587235032284965E-3</c:v>
+                  <c:v>3.4422129045198948E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.0633294620639323E-3</c:v>
+                  <c:v>4.2886612468895045E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.7570772335819985E-3</c:v>
+                  <c:v>5.2599081270147978E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>4.5449444623392177E-3</c:v>
+                  <c:v>6.3629222472749046E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.4315290673835337E-3</c:v>
+                  <c:v>7.604140694336947E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>6.4210050770837218E-3</c:v>
+                  <c:v>8.9894071079172095E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.5170782388275237E-3</c:v>
+                  <c:v>1.0523909534358533E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8.7229420039149769E-3</c:v>
+                  <c:v>1.2212118805480968E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.0041234530816401E-2</c:v>
+                  <c:v>1.405772834314296E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.1473997386527171E-2</c:v>
+                  <c:v>1.6063596341138037E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.3022636654488842E-2</c:v>
+                  <c:v>1.8231691316284378E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.4687887176925568E-2</c:v>
+                  <c:v>2.0563042047695795E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.6469780667991457E-2</c:v>
+                  <c:v>2.3057692935188039E-2</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.8367618430465693E-2</c:v>
+                  <c:v>2.571466580265197E-2</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>2.0379949391649221E-2</c:v>
+                  <c:v>2.8531929148308908E-2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2.2504554142594765E-2</c:v>
+                  <c:v>3.1506375799632669E-2</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.4738435618083782E-2</c:v>
+                  <c:v>3.4633809865317292E-2</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.7077816992397724E-2</c:v>
+                  <c:v>3.790894378935681E-2</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.951814728782165E-2</c:v>
+                  <c:v>4.1325406202950304E-2</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>3.2054115099261718E-2</c:v>
+                  <c:v>4.4875761138966401E-2</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>3.467967073008181E-2</c:v>
+                  <c:v>4.855153902211453E-2</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>3.7388056912446274E-2</c:v>
+                  <c:v>5.2343279677424782E-2</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4.0171848151733677E-2</c:v>
+                  <c:v>5.6240587412427143E-2</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.3022998591062303E-2</c:v>
+                  <c:v>6.0232198027487222E-2</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4.5932898141179429E-2</c:v>
+                  <c:v>6.4306057397651203E-2</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4.8892436465861083E-2</c:v>
+                  <c:v>6.8449411052205505E-2</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5.1892074256846804E-2</c:v>
+                  <c:v>7.2648903959585523E-2</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5.4921921078778663E-2</c:v>
+                  <c:v>7.6890689510290128E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2145,6 +2146,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2152,7 +2154,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4273,28 +4274,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3D2DEE-686E-48A0-AC3D-0F54DEA5D0EC}">
   <dimension ref="A1:C124"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="88.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="88.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -4302,48 +4303,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -4351,7 +4352,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -4359,7 +4360,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -4367,15 +4368,15 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>39</v>
       </c>
       <c r="B19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23">
         <f>(1-EXP(-((C23/$B$19-($B$18-0.5))/$B$16)^$B$17))*$B$15</f>
         <v>0</v>
@@ -4384,1014 +4385,1012 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24">
         <f t="shared" ref="B24:B87" si="0">(1-EXP(-((C24/$B$19-($B$18-0.5))/$B$16)^$B$17))*$B$15</f>
-        <v>1.1302755611730664E-6</v>
+        <v>4.688565392790833E-7</v>
       </c>
       <c r="C24">
-        <f>C23+0.25</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B25">
         <f t="shared" si="0"/>
-        <v>9.041918329455445E-6</v>
+        <v>3.7508171421674062E-6</v>
       </c>
       <c r="C25">
-        <f t="shared" ref="C25:C88" si="1">C24+0.25</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26">
         <f t="shared" si="0"/>
-        <v>3.0513853137847935E-5</v>
+        <v>1.2658685661237622E-5</v>
       </c>
       <c r="C26">
-        <f t="shared" si="1"/>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <f>C25+500</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27">
         <f t="shared" si="0"/>
-        <v>7.2317035876470759E-5</v>
+        <v>3.0004286253101917E-5</v>
       </c>
       <c r="C27">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <f t="shared" ref="C27:C90" si="1">C26+500</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28">
         <f t="shared" si="0"/>
-        <v>1.4120526808655831E-4</v>
+        <v>5.8597333307211504E-5</v>
       </c>
       <c r="C28">
         <f t="shared" si="1"/>
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29">
         <f t="shared" si="0"/>
-        <v>2.4390236156555944E-4</v>
+        <v>1.0124385022705905E-4</v>
       </c>
       <c r="C29">
         <f t="shared" si="1"/>
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B30">
         <f t="shared" si="0"/>
-        <v>3.8708568873771498E-4</v>
+        <v>1.607441383691538E-4</v>
       </c>
       <c r="C30">
         <f t="shared" si="1"/>
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31">
         <f t="shared" si="0"/>
-        <v>5.7736617667798751E-4</v>
+        <v>2.3989029825592642E-4</v>
       </c>
       <c r="C31">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32">
         <f t="shared" si="0"/>
-        <v>8.2126483012147367E-4</v>
+        <v>3.4146330619178321E-4</v>
       </c>
       <c r="C32">
         <f t="shared" si="1"/>
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33">
         <f t="shared" si="0"/>
-        <v>1.1251859013301779E-3</v>
+        <v>4.6822965062173478E-4</v>
       </c>
       <c r="C33">
         <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34">
         <f t="shared" si="0"/>
-        <v>1.4953868620252581E-3</v>
+        <v>6.229375339770665E-4</v>
       </c>
       <c r="C34">
         <f t="shared" si="1"/>
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35">
         <f t="shared" si="0"/>
-        <v>1.9379453743239433E-3</v>
+        <v>8.0831264734918245E-4</v>
       </c>
       <c r="C35">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36">
         <f t="shared" si="0"/>
-        <v>2.4587235032284965E-3</v>
+        <v>1.0270535271122315E-3</v>
       </c>
       <c r="C36">
         <f t="shared" si="1"/>
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B37">
         <f t="shared" si="0"/>
-        <v>3.0633294620639323E-3</v>
+        <v>1.2818265045742155E-3</v>
       </c>
       <c r="C37">
         <f t="shared" si="1"/>
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38">
         <f t="shared" si="0"/>
-        <v>3.7570772335819985E-3</v>
+        <v>1.5752602618622491E-3</v>
       </c>
       <c r="C38">
         <f t="shared" si="1"/>
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B39">
         <f t="shared" si="0"/>
-        <v>4.5449444623392177E-3</v>
+        <v>1.9099400095324429E-3</v>
       </c>
       <c r="C39">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40">
         <f t="shared" si="0"/>
-        <v>5.4315290673835337E-3</v>
+        <v>2.288401303826018E-3</v>
       </c>
       <c r="C40">
         <f t="shared" si="1"/>
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B41">
         <f t="shared" si="0"/>
-        <v>6.4210050770837218E-3</v>
+        <v>2.7131235240535206E-3</v>
       </c>
       <c r="C41">
         <f t="shared" si="1"/>
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B42">
         <f t="shared" si="0"/>
-        <v>7.5170782388275237E-3</v>
+        <v>3.1865230332662389E-3</v>
       </c>
       <c r="C42">
         <f t="shared" si="1"/>
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B43">
         <f t="shared" si="0"/>
-        <v>8.7229420039149769E-3</v>
+        <v>3.710946048145702E-3</v>
       </c>
       <c r="C43">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B44">
         <f t="shared" si="0"/>
-        <v>1.0041234530816401E-2</v>
+        <v>4.2886612468895045E-3</v>
       </c>
       <c r="C44">
         <f t="shared" si="1"/>
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B45">
         <f t="shared" si="0"/>
-        <v>1.1473997386527171E-2</v>
+        <v>4.9218521467715125E-3</v>
       </c>
       <c r="C45">
         <f t="shared" si="1"/>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B46">
         <f t="shared" si="0"/>
-        <v>1.3022636654488842E-2</v>
+        <v>5.6126092859814757E-3</v>
       </c>
       <c r="C46">
         <f t="shared" si="1"/>
-        <v>5.75</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B47">
         <f t="shared" si="0"/>
-        <v>1.4687887176925568E-2</v>
+        <v>6.3629222472749046E-3</v>
       </c>
       <c r="C47">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B48">
         <f t="shared" si="0"/>
-        <v>1.6469780667991457E-2</v>
+        <v>7.1746715638626715E-3</v>
       </c>
       <c r="C48">
         <f t="shared" si="1"/>
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B49">
         <f t="shared" si="0"/>
-        <v>1.8367618430465693E-2</v>
+        <v>8.0496205508047858E-3</v>
       </c>
       <c r="C49">
         <f t="shared" si="1"/>
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B50">
         <f t="shared" si="0"/>
-        <v>2.0379949391649221E-2</v>
+        <v>8.9894071079172095E-3</v>
       </c>
       <c r="C50">
         <f t="shared" si="1"/>
-        <v>6.75</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B51">
         <f t="shared" si="0"/>
-        <v>2.2504554142594765E-2</v>
+        <v>9.9955355428148346E-3</v>
       </c>
       <c r="C51">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B52">
         <f t="shared" si="0"/>
-        <v>2.4738435618083782E-2</v>
+        <v>1.1069368465165541E-2</v>
       </c>
       <c r="C52">
         <f t="shared" si="1"/>
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B53">
         <f t="shared" si="0"/>
-        <v>2.7077816992397724E-2</v>
+        <v>1.2212118805480968E-2</v>
       </c>
       <c r="C53">
         <f t="shared" si="1"/>
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B54">
         <f t="shared" si="0"/>
-        <v>2.951814728782165E-2</v>
+        <v>1.3424842013782658E-2</v>
       </c>
       <c r="C54">
         <f t="shared" si="1"/>
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B55">
         <f t="shared" si="0"/>
-        <v>3.2054115099261718E-2</v>
+        <v>1.4708428495219757E-2</v>
       </c>
       <c r="C55">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B56">
         <f t="shared" si="0"/>
-        <v>3.467967073008181E-2</v>
+        <v>1.6063596341138037E-2</v>
       </c>
       <c r="C56">
         <f t="shared" si="1"/>
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B57">
         <f t="shared" si="0"/>
-        <v>3.7388056912446274E-2</v>
+        <v>1.7490884415174143E-2</v>
       </c>
       <c r="C57">
         <f t="shared" si="1"/>
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B58">
         <f t="shared" si="0"/>
-        <v>4.0171848151733677E-2</v>
+        <v>1.899064585463596E-2</v>
       </c>
       <c r="C58">
         <f t="shared" si="1"/>
-        <v>8.75</v>
-      </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B59">
         <f t="shared" si="0"/>
-        <v>4.3022998591062303E-2</v>
+        <v>2.0563042047695795E-2</v>
       </c>
       <c r="C59">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B60">
         <f t="shared" si="0"/>
-        <v>4.5932898141179429E-2</v>
+        <v>2.2208037146736314E-2</v>
       </c>
       <c r="C60">
         <f t="shared" si="1"/>
-        <v>9.25</v>
-      </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+        <v>18500</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B61">
         <f t="shared" si="0"/>
-        <v>4.8892436465861083E-2</v>
+        <v>2.3925393177517337E-2</v>
       </c>
       <c r="C61">
         <f t="shared" si="1"/>
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B62">
         <f t="shared" si="0"/>
-        <v>5.1892074256846804E-2</v>
+        <v>2.571466580265197E-2</v>
       </c>
       <c r="C62">
         <f t="shared" si="1"/>
-        <v>9.75</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B63">
         <f t="shared" si="0"/>
-        <v>5.4921921078778663E-2</v>
+        <v>2.7575200796164531E-2</v>
       </c>
       <c r="C63">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B64">
         <f t="shared" si="0"/>
-        <v>5.7971818917411488E-2</v>
+        <v>2.9506131283638978E-2</v>
       </c>
       <c r="C64">
         <f t="shared" si="1"/>
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+        <v>20500</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B65">
         <f t="shared" si="0"/>
-        <v>6.1031430427395852E-2</v>
+        <v>3.1506375799632669E-2</v>
       </c>
       <c r="C65">
         <f t="shared" si="1"/>
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B66">
         <f t="shared" si="0"/>
-        <v>6.4090330753079128E-2</v>
+        <v>3.357463721062659E-2</v>
       </c>
       <c r="C66">
         <f t="shared" si="1"/>
-        <v>10.75</v>
-      </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B67">
         <f t="shared" si="0"/>
-        <v>6.7138101690766061E-2</v>
+        <v>3.5709402547799238E-2</v>
       </c>
       <c r="C67">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B68">
         <f t="shared" si="0"/>
-        <v>7.0164426877205852E-2</v>
+        <v>3.790894378935681E-2</v>
       </c>
       <c r="C68">
         <f t="shared" si="1"/>
-        <v>11.25</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B69">
         <f t="shared" si="0"/>
-        <v>7.3159186629829842E-2</v>
+        <v>4.0171319627034394E-2</v>
       </c>
       <c r="C69">
         <f t="shared" si="1"/>
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B70">
         <f t="shared" si="0"/>
-        <v>7.6112551032035736E-2</v>
+        <v>4.2494378245719382E-2</v>
       </c>
       <c r="C70">
         <f t="shared" si="1"/>
-        <v>11.75</v>
-      </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B71">
         <f t="shared" si="0"/>
-        <v>7.9015069853569708E-2</v>
+        <v>4.4875761138966401E-2</v>
       </c>
       <c r="C71">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B72">
         <f t="shared" si="0"/>
-        <v>8.1857757923041286E-2</v>
+        <v>4.7312907976500215E-2</v>
       </c>
       <c r="C72">
         <f t="shared" si="1"/>
-        <v>12.25</v>
-      </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B73">
         <f t="shared" si="0"/>
-        <v>8.4632174627258694E-2</v>
+        <v>4.9803062532686002E-2</v>
       </c>
       <c r="C73">
         <f t="shared" si="1"/>
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B74">
         <f t="shared" si="0"/>
-        <v>8.7330496299984461E-2</v>
+        <v>5.2343279677424782E-2</v>
       </c>
       <c r="C74">
         <f t="shared" si="1"/>
-        <v>12.75</v>
-      </c>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+        <v>25500</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B75">
         <f t="shared" si="0"/>
-        <v>8.9945580379575493E-2</v>
+        <v>5.4930433423066853E-2</v>
       </c>
       <c r="C75">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B76">
         <f t="shared" si="0"/>
-        <v>9.2471020358609296E-2</v>
+        <v>5.7561226012785335E-2</v>
       </c>
       <c r="C76">
         <f t="shared" si="1"/>
-        <v>13.25</v>
-      </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+        <v>26500</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B77">
         <f t="shared" si="0"/>
-        <v>9.4901190715968961E-2</v>
+        <v>6.0232198027487222E-2</v>
       </c>
       <c r="C77">
         <f t="shared" si="1"/>
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B78">
         <f t="shared" si="0"/>
-        <v>9.7231281209145953E-2</v>
+        <v>6.2939739479831808E-2</v>
       </c>
       <c r="C78">
         <f t="shared" si="1"/>
-        <v>13.75</v>
-      </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+        <v>27500</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B79">
         <f t="shared" si="0"/>
-        <v>9.9457320107219804E-2</v>
+        <v>6.5680101855361245E-2</v>
       </c>
       <c r="C79">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B80">
         <f t="shared" si="0"/>
-        <v>0.10157618615802415</v>
+        <v>6.8449411052205505E-2</v>
       </c>
       <c r="C80">
         <f t="shared" si="1"/>
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+        <v>28500</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B81">
         <f t="shared" si="0"/>
-        <v>0.1035856093009499</v>
+        <v>7.1243681162399208E-2</v>
       </c>
       <c r="C81">
         <f t="shared" si="1"/>
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B82">
         <f t="shared" si="0"/>
-        <v>0.10548416035397182</v>
+        <v>7.4058829029625878E-2</v>
       </c>
       <c r="C82">
         <f t="shared" si="1"/>
-        <v>14.75</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+        <v>29500</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B83">
         <f t="shared" si="0"/>
-        <v>0.10727123011408218</v>
+        <v>7.6890689510290128E-2</v>
       </c>
       <c r="C83">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B84">
         <f t="shared" si="0"/>
-        <v>0.10894699850878881</v>
+        <v>7.9735031357294192E-2</v>
       </c>
       <c r="C84">
         <f t="shared" si="1"/>
-        <v>15.25</v>
-      </c>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+        <v>30500</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B85">
         <f t="shared" si="0"/>
-        <v>0.11051239461744319</v>
+        <v>8.2587573638868067E-2</v>
       </c>
       <c r="C85">
         <f t="shared" si="1"/>
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B86">
         <f t="shared" si="0"/>
-        <v>0.11196904854019522</v>
+        <v>8.5444002598354191E-2</v>
       </c>
       <c r="C86">
         <f t="shared" si="1"/>
-        <v>15.75</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+        <v>31500</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B87">
         <f t="shared" si="0"/>
-        <v>0.11331923622529684</v>
+        <v>8.8299988855078684E-2</v>
       </c>
       <c r="C87">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B88">
         <f t="shared" ref="B88:B124" si="2">(1-EXP(-((C88/$B$19-($B$18-0.5))/$B$16)^$B$17))*$B$15</f>
-        <v>0.11456581846910648</v>
+        <v>9.1151204841427483E-2</v>
       </c>
       <c r="C88">
         <f t="shared" si="1"/>
-        <v>16.25</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B89">
         <f t="shared" si="2"/>
-        <v>0.11571217537522674</v>
+        <v>9.3993342367072477E-2</v>
       </c>
       <c r="C89">
-        <f t="shared" ref="C89:C124" si="3">C88+0.25</f>
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B90">
         <f t="shared" si="2"/>
-        <v>0.11676213759849677</v>
+        <v>9.6822130198030765E-2</v>
       </c>
       <c r="C90">
-        <f t="shared" si="3"/>
-        <v>16.75</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>33500</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B91">
         <f t="shared" si="2"/>
-        <v>0.11771991570586685</v>
+        <v>9.9633351535951209E-2</v>
       </c>
       <c r="C91">
-        <f t="shared" si="3"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+        <f t="shared" ref="C91:C124" si="3">C90+500</f>
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B92">
         <f t="shared" si="2"/>
-        <v>0.11859002896034841</v>
+        <v>0.10242286128176177</v>
       </c>
       <c r="C92">
         <f t="shared" si="3"/>
-        <v>17.25</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+        <v>34500</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B93">
         <f t="shared" si="2"/>
-        <v>0.11937723477809242</v>
+        <v>0.10518660296762164</v>
       </c>
       <c r="C93">
         <f t="shared" si="3"/>
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B94">
         <f t="shared" si="2"/>
-        <v>0.12008646002494117</v>
+        <v>0.10792062524203296</v>
       </c>
       <c r="C94">
         <f t="shared" si="3"/>
-        <v>17.75</v>
-      </c>
-    </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+        <v>35500</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B95">
         <f t="shared" si="2"/>
-        <v>0.12072273521104175</v>
+        <v>0.11062109779499758</v>
       </c>
       <c r="C95">
         <f t="shared" si="3"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+        <v>36000</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B96">
         <f t="shared" si="2"/>
-        <v>0.12129113251445571</v>
+        <v>0.11328432661325752</v>
       </c>
       <c r="C96">
         <f t="shared" si="3"/>
-        <v>18.25</v>
-      </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+        <v>36500</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B97">
         <f t="shared" si="2"/>
-        <v>0.12179670842176366</v>
+        <v>0.11590676845992481</v>
       </c>
       <c r="C97">
         <f t="shared" si="3"/>
-        <v>18.5</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B98">
         <f t="shared" si="2"/>
-        <v>0.12224445162033554</v>
+        <v>0.11848504447816216</v>
       </c>
       <c r="C98">
         <f t="shared" si="3"/>
-        <v>18.75</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+        <v>37500</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B99">
         <f t="shared" si="2"/>
-        <v>0.12263923661819812</v>
+        <v>0.12101595282498293</v>
       </c>
       <c r="C99">
         <f t="shared" si="3"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B100">
         <f t="shared" si="2"/>
-        <v>0.12298578340816241</v>
+        <v>0.12349648024863966</v>
       </c>
       <c r="C100">
         <f t="shared" si="3"/>
-        <v>19.25</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+        <v>38500</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B101">
         <f t="shared" si="2"/>
-        <v>0.12328862333768843</v>
+        <v>0.12592381253140569</v>
       </c>
       <c r="C101">
         <f t="shared" si="3"/>
-        <v>19.5</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+        <v>39000</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B102">
         <f t="shared" si="2"/>
-        <v>0.12355207119904957</v>
+        <v>0.12829534372873438</v>
       </c>
       <c r="C102">
         <f t="shared" si="3"/>
-        <v>19.75</v>
-      </c>
-    </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+        <v>39500</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B103">
         <f t="shared" si="2"/>
-        <v>0.12378020341934777</v>
+        <v>0.13060868414571794</v>
       </c>
       <c r="C103">
         <f t="shared" si="3"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B104">
         <f t="shared" si="2"/>
-        <v>0.1239768421098045</v>
+        <v>0.13286166700235655</v>
       </c>
       <c r="C104">
         <f t="shared" si="3"/>
-        <v>20.25</v>
-      </c>
-    </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+        <v>40500</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B105">
         <f t="shared" si="2"/>
-        <v>0.12414554463077215</v>
+        <v>0.13505235375027189</v>
       </c>
       <c r="C105">
         <f t="shared" si="3"/>
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B106">
         <f t="shared" si="2"/>
-        <v>0.12428959824458628</v>
+        <v>0.13717903801503675</v>
       </c>
       <c r="C106">
         <f t="shared" si="3"/>
-        <v>20.75</v>
-      </c>
-    </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+        <v>41500</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B107">
         <f t="shared" si="2"/>
-        <v>0.12441201936347031</v>
+        <v>0.13924024815010771</v>
       </c>
       <c r="C107">
         <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B108">
         <f t="shared" si="2"/>
-        <v>0.12451555685425303</v>
+        <v>0.14123474840031372</v>
       </c>
       <c r="C108">
         <f t="shared" si="3"/>
-        <v>21.25</v>
-      </c>
-    </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B109">
         <f t="shared" si="2"/>
-        <v>0.12460269883504811</v>
+        <v>0.14316153868482104</v>
       </c>
       <c r="C109">
         <f t="shared" si="3"/>
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B110">
         <f t="shared" si="2"/>
-        <v>0.12467568239008178</v>
+        <v>0.14501985302132986</v>
       </c>
       <c r="C110">
         <f t="shared" si="3"/>
-        <v>21.75</v>
-      </c>
-    </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+        <v>43500</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B111">
         <f t="shared" si="2"/>
-        <v>0.12473650563587114</v>
+        <v>0.1468091566248198</v>
       </c>
       <c r="C111">
         <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B112">
         <f t="shared" si="2"/>
-        <v>0.12478694159291652</v>
+        <v>0.14852914172531101</v>
       </c>
       <c r="C112">
         <f t="shared" si="3"/>
-        <v>22.25</v>
-      </c>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+        <v>44500</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B113">
         <f t="shared" si="2"/>
-        <v>0.12482855334969299</v>
+        <v>0.15017972215971503</v>
       </c>
       <c r="C113">
         <f t="shared" si="3"/>
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B114">
         <f t="shared" si="2"/>
-        <v>0.12486271004758752</v>
+        <v>0.15176102680279263</v>
       </c>
       <c r="C114">
         <f t="shared" si="3"/>
-        <v>22.75</v>
-      </c>
-    </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+        <v>45500</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B115">
         <f t="shared" si="2"/>
-        <v>0.12489060326408261</v>
+        <v>0.15327339191139272</v>
       </c>
       <c r="C115">
         <f t="shared" si="3"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B116">
         <f t="shared" si="2"/>
-        <v>0.12491326342455751</v>
+        <v>0.15471735246442045</v>
       </c>
       <c r="C116">
         <f t="shared" si="3"/>
-        <v>23.25</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+        <v>46500</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B117">
         <f t="shared" si="2"/>
-        <v>0.12493157592833935</v>
+        <v>0.15609363258827613</v>
       </c>
       <c r="C117">
         <f t="shared" si="3"/>
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B118">
         <f t="shared" si="2"/>
-        <v>0.12494629673008874</v>
+        <v>0.15740313516374241</v>
       </c>
       <c r="C118">
         <f t="shared" si="3"/>
-        <v>23.75</v>
-      </c>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+        <v>47500</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B119">
         <f t="shared" si="2"/>
-        <v>0.12495806717151219</v>
+        <v>0.15864693071541558</v>
       </c>
       <c r="C119">
         <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B120">
         <f t="shared" si="2"/>
-        <v>0.12496742790932699</v>
+        <v>0.15982624568872567</v>
       </c>
       <c r="C120">
         <f t="shared" si="3"/>
-        <v>24.25</v>
-      </c>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+        <v>48500</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B121">
         <f t="shared" si="2"/>
-        <v>0.1249748318322462</v>
+        <v>0.16094245022234396</v>
       </c>
       <c r="C121">
         <f t="shared" si="3"/>
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B122">
         <f t="shared" si="2"/>
-        <v>0.12498065590169766</v>
+        <v>0.16199704552531743</v>
       </c>
       <c r="C122">
         <f t="shared" si="3"/>
-        <v>24.75</v>
-      </c>
-    </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+        <v>49500</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B123">
         <f t="shared" si="2"/>
-        <v>0.12498521188753921</v>
+        <v>0.16299165096860699</v>
       </c>
       <c r="C123">
         <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B124">
         <f t="shared" si="2"/>
-        <v>0.1249887560009456</v>
+        <v>0.16392799099985553</v>
       </c>
       <c r="C124">
         <f t="shared" si="3"/>
-        <v>25.25</v>
+        <v>50500</v>
       </c>
     </row>
   </sheetData>
@@ -5406,13 +5405,13 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:CF2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:84" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:84" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -5422,334 +5421,334 @@
       </c>
       <c r="C1">
         <f>(1-EXP(-((C2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.1302755611730664E-6</v>
+        <v>1.5823857856422929E-6</v>
       </c>
       <c r="D1">
         <f>(1-EXP(-((D2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>9.041918329455445E-6</v>
+        <v>1.2658685661237622E-5</v>
       </c>
       <c r="E1">
         <f>(1-EXP(-((E2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>3.0513853137847935E-5</v>
+        <v>4.2719394392987109E-5</v>
       </c>
       <c r="F1">
         <f>(1-EXP(-((F2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>7.2317035876470759E-5</v>
+        <v>1.0124385022705905E-4</v>
       </c>
       <c r="G1">
         <f>(1-EXP(-((G2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.4120526808655831E-4</v>
+        <v>1.9768737532118162E-4</v>
       </c>
       <c r="H1">
         <f>(1-EXP(-((H2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>2.4390236156555944E-4</v>
+        <v>3.4146330619178321E-4</v>
       </c>
       <c r="I1">
         <f>(1-EXP(-((I2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>3.8708568873771498E-4</v>
+        <v>5.4191996423280089E-4</v>
       </c>
       <c r="J1">
         <f>(1-EXP(-((J2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>5.7736617667798751E-4</v>
+        <v>8.0831264734918245E-4</v>
       </c>
       <c r="K1">
         <f>(1-EXP(-((K2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>8.2126483012147367E-4</v>
+        <v>1.149770762170063E-3</v>
       </c>
       <c r="L1">
         <f>(1-EXP(-((L2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.1251859013301779E-3</v>
+        <v>1.5752602618622491E-3</v>
       </c>
       <c r="M1">
         <f>(1-EXP(-((M2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.4953868620252581E-3</v>
+        <v>2.093541606835361E-3</v>
       </c>
       <c r="N1">
         <f>(1-EXP(-((N2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.9379453743239433E-3</v>
+        <v>2.7131235240535206E-3</v>
       </c>
       <c r="O1">
         <f>(1-EXP(-((O2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>2.4587235032284965E-3</v>
+        <v>3.4422129045198948E-3</v>
       </c>
       <c r="P1">
         <f>(1-EXP(-((P2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>3.0633294620639323E-3</v>
+        <v>4.2886612468895045E-3</v>
       </c>
       <c r="Q1">
         <f>(1-EXP(-((Q2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>3.7570772335819985E-3</v>
+        <v>5.2599081270147978E-3</v>
       </c>
       <c r="R1">
         <f>(1-EXP(-((R2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>4.5449444623392177E-3</v>
+        <v>6.3629222472749046E-3</v>
       </c>
       <c r="S1">
         <f>(1-EXP(-((S2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>5.4315290673835337E-3</v>
+        <v>7.604140694336947E-3</v>
       </c>
       <c r="T1">
         <f>(1-EXP(-((T2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>6.4210050770837218E-3</v>
+        <v>8.9894071079172095E-3</v>
       </c>
       <c r="U1">
         <f>(1-EXP(-((U2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>7.5170782388275237E-3</v>
+        <v>1.0523909534358533E-2</v>
       </c>
       <c r="V1">
         <f>(1-EXP(-((V2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>8.7229420039149769E-3</v>
+        <v>1.2212118805480968E-2</v>
       </c>
       <c r="W1">
         <f>(1-EXP(-((W2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.0041234530816401E-2</v>
+        <v>1.405772834314296E-2</v>
       </c>
       <c r="X1">
         <f>(1-EXP(-((X2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.1473997386527171E-2</v>
+        <v>1.6063596341138037E-2</v>
       </c>
       <c r="Y1">
         <f>(1-EXP(-((Y2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.3022636654488842E-2</v>
+        <v>1.8231691316284378E-2</v>
       </c>
       <c r="Z1">
         <f>(1-EXP(-((Z2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.4687887176925568E-2</v>
+        <v>2.0563042047695795E-2</v>
       </c>
       <c r="AA1">
         <f>(1-EXP(-((AA2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.6469780667991457E-2</v>
+        <v>2.3057692935188039E-2</v>
       </c>
       <c r="AB1">
         <f>(1-EXP(-((AB2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>1.8367618430465693E-2</v>
+        <v>2.571466580265197E-2</v>
       </c>
       <c r="AC1">
         <f>(1-EXP(-((AC2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>2.0379949391649221E-2</v>
+        <v>2.8531929148308908E-2</v>
       </c>
       <c r="AD1">
         <f>(1-EXP(-((AD2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>2.2504554142594765E-2</v>
+        <v>3.1506375799632669E-2</v>
       </c>
       <c r="AE1">
         <f>(1-EXP(-((AE2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>2.4738435618083782E-2</v>
+        <v>3.4633809865317292E-2</v>
       </c>
       <c r="AF1">
         <f>(1-EXP(-((AF2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>2.7077816992397724E-2</v>
+        <v>3.790894378935681E-2</v>
       </c>
       <c r="AG1">
         <f>(1-EXP(-((AG2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>2.951814728782165E-2</v>
+        <v>4.1325406202950304E-2</v>
       </c>
       <c r="AH1">
         <f>(1-EXP(-((AH2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>3.2054115099261718E-2</v>
+        <v>4.4875761138966401E-2</v>
       </c>
       <c r="AI1">
         <f>(1-EXP(-((AI2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>3.467967073008181E-2</v>
+        <v>4.855153902211453E-2</v>
       </c>
       <c r="AJ1">
         <f>(1-EXP(-((AJ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>3.7388056912446274E-2</v>
+        <v>5.2343279677424782E-2</v>
       </c>
       <c r="AK1">
         <f>(1-EXP(-((AK2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>4.0171848151733677E-2</v>
+        <v>5.6240587412427143E-2</v>
       </c>
       <c r="AL1">
         <f>(1-EXP(-((AL2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>4.3022998591062303E-2</v>
+        <v>6.0232198027487222E-2</v>
       </c>
       <c r="AM1">
         <f>(1-EXP(-((AM2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>4.5932898141179429E-2</v>
+        <v>6.4306057397651203E-2</v>
       </c>
       <c r="AN1">
         <f>(1-EXP(-((AN2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>4.8892436465861083E-2</v>
+        <v>6.8449411052205505E-2</v>
       </c>
       <c r="AO1">
         <f>(1-EXP(-((AO2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>5.1892074256846804E-2</v>
+        <v>7.2648903959585523E-2</v>
       </c>
       <c r="AP1">
         <f>(1-EXP(-((AP2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>5.4921921078778663E-2</v>
+        <v>7.6890689510290128E-2</v>
       </c>
       <c r="AQ1">
         <f>(1-EXP(-((AQ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>5.7971818917411488E-2</v>
+        <v>8.1160546484376081E-2</v>
       </c>
       <c r="AR1">
         <f>(1-EXP(-((AR2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>6.1031430427395852E-2</v>
+        <v>8.5444002598354191E-2</v>
       </c>
       <c r="AS1">
         <f>(1-EXP(-((AS2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>6.4090330753079128E-2</v>
+        <v>8.9726463054310771E-2</v>
       </c>
       <c r="AT1">
         <f>(1-EXP(-((AT2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>6.7138101690766061E-2</v>
+        <v>9.3993342367072477E-2</v>
       </c>
       <c r="AU1">
         <f>(1-EXP(-((AU2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>7.0164426877205852E-2</v>
+        <v>9.8230197628088184E-2</v>
       </c>
       <c r="AV1">
         <f>(1-EXP(-((AV2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>7.3159186629829842E-2</v>
+        <v>0.10242286128176177</v>
       </c>
       <c r="AW1">
         <f>(1-EXP(-((AW2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>7.6112551032035736E-2</v>
+        <v>0.10655757144485002</v>
       </c>
       <c r="AX1">
         <f>(1-EXP(-((AX2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>7.9015069853569708E-2</v>
+        <v>0.11062109779499758</v>
       </c>
       <c r="AY1">
         <f>(1-EXP(-((AY2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>8.1857757923041286E-2</v>
+        <v>0.1146008610922578</v>
       </c>
       <c r="AZ1">
         <f>(1-EXP(-((AZ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>8.4632174627258694E-2</v>
+        <v>0.11848504447816216</v>
       </c>
       <c r="BA1">
         <f>(1-EXP(-((BA2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>8.7330496299984461E-2</v>
+        <v>0.12226269481997824</v>
       </c>
       <c r="BB1">
         <f>(1-EXP(-((BB2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>8.9945580379575493E-2</v>
+        <v>0.12592381253140569</v>
       </c>
       <c r="BC1">
         <f>(1-EXP(-((BC2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>9.2471020358609296E-2</v>
+        <v>0.129459428502053</v>
       </c>
       <c r="BD1">
         <f>(1-EXP(-((BD2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>9.4901190715968961E-2</v>
+        <v>0.13286166700235655</v>
       </c>
       <c r="BE1">
         <f>(1-EXP(-((BE2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>9.7231281209145953E-2</v>
+        <v>0.13612379369280433</v>
       </c>
       <c r="BF1">
         <f>(1-EXP(-((BF2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>9.9457320107219804E-2</v>
+        <v>0.13924024815010771</v>
       </c>
       <c r="BG1">
         <f>(1-EXP(-((BG2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.10157618615802415</v>
+        <v>0.1422066606212338</v>
       </c>
       <c r="BH1">
         <f>(1-EXP(-((BH2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.1035856093009499</v>
+        <v>0.14501985302132986</v>
       </c>
       <c r="BI1">
         <f>(1-EXP(-((BI2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.10548416035397182</v>
+        <v>0.14767782449556052</v>
       </c>
       <c r="BJ1">
         <f>(1-EXP(-((BJ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.10727123011408218</v>
+        <v>0.15017972215971503</v>
       </c>
       <c r="BK1">
         <f>(1-EXP(-((BK2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.10894699850878881</v>
+        <v>0.15252579791230431</v>
       </c>
       <c r="BL1">
         <f>(1-EXP(-((BL2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.11051239461744319</v>
+        <v>0.15471735246442045</v>
       </c>
       <c r="BM1">
         <f>(1-EXP(-((BM2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.11196904854019522</v>
+        <v>0.1567566679562733</v>
       </c>
       <c r="BN1">
         <f>(1-EXP(-((BN2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.11331923622529684</v>
+        <v>0.15864693071541558</v>
       </c>
       <c r="BO1">
         <f>(1-EXP(-((BO2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.11456581846910648</v>
+        <v>0.16039214585674905</v>
       </c>
       <c r="BP1">
         <f>(1-EXP(-((BP2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.11571217537522674</v>
+        <v>0.16199704552531743</v>
       </c>
       <c r="BQ1">
         <f>(1-EXP(-((BQ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.11676213759849677</v>
+        <v>0.16346699263789546</v>
       </c>
       <c r="BR1">
         <f>(1-EXP(-((BR2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.11771991570586685</v>
+        <v>0.16480788198821358</v>
       </c>
       <c r="BS1">
         <f>(1-EXP(-((BS2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.11859002896034841</v>
+        <v>0.16602604054448777</v>
       </c>
       <c r="BT1">
         <f>(1-EXP(-((BT2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.11937723477809242</v>
+        <v>0.16712812868932939</v>
       </c>
       <c r="BU1">
         <f>(1-EXP(-((BU2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12008646002494117</v>
+        <v>0.16812104403491762</v>
       </c>
       <c r="BV1">
         <f>(1-EXP(-((BV2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12072273521104175</v>
+        <v>0.16901182929545844</v>
       </c>
       <c r="BW1">
         <f>(1-EXP(-((BW2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12129113251445571</v>
+        <v>0.16980758552023797</v>
       </c>
       <c r="BX1">
         <f>(1-EXP(-((BX2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12179670842176366</v>
+        <v>0.1705153917904691</v>
       </c>
       <c r="BY1">
         <f>(1-EXP(-((BY2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12224445162033554</v>
+        <v>0.17114223226846975</v>
       </c>
       <c r="BZ1">
         <f>(1-EXP(-((BZ2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12263923661819812</v>
+        <v>0.17169493126547736</v>
       </c>
       <c r="CA1">
         <f>(1-EXP(-((CA2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12298578340816241</v>
+        <v>0.17218009677142737</v>
       </c>
       <c r="CB1">
         <f>(1-EXP(-((CB2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12328862333768843</v>
+        <v>0.17260407267276379</v>
       </c>
       <c r="CC1">
         <f>(1-EXP(-((CC2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12355207119904957</v>
+        <v>0.17297289967866938</v>
       </c>
       <c r="CD1">
         <f>(1-EXP(-((CD2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.12378020341934777</v>
+        <v>0.17329228478708686</v>
       </c>
       <c r="CE1">
         <f>(1-EXP(-((CE2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.125</v>
+        <v>0.17356757895372629</v>
       </c>
       <c r="CF1">
         <f>(1-EXP(-((CF2/About!$B$19-(About!$B$18-0.5))/About!$B$16)^About!$B$17))*About!$B$15</f>
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:84" x14ac:dyDescent="0.25">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="2" spans="1:84" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -5757,330 +5756,331 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <f>B2+0.25</f>
-        <v>0.25</v>
+        <f>B2+750</f>
+        <v>750</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:AI2" si="0">C2+0.25</f>
-        <v>0.5</v>
+        <f t="shared" ref="D2:BO2" si="0">C2+750</f>
+        <v>1500</v>
       </c>
       <c r="E2">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>2250</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3000</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>1.25</v>
+        <v>3750</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>4500</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>1.75</v>
+        <v>5250</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>6000</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>6750</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>7500</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>2.75</v>
+        <v>8250</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>9000</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>3.25</v>
+        <v>9750</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>3.5</v>
+        <v>10500</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>3.75</v>
+        <v>11250</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>12000</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>4.25</v>
+        <v>12750</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>13500</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>4.75</v>
+        <v>14250</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>15000</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>5.25</v>
+        <v>15750</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>5.5</v>
+        <v>16500</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>5.75</v>
+        <v>17250</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>18000</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>6.25</v>
+        <v>18750</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>19500</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>6.75</v>
+        <v>20250</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>21000</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>7.25</v>
+        <v>21750</v>
       </c>
       <c r="AF2">
         <f t="shared" si="0"/>
-        <v>7.5</v>
+        <v>22500</v>
       </c>
       <c r="AG2">
         <f t="shared" si="0"/>
-        <v>7.75</v>
+        <v>23250</v>
       </c>
       <c r="AH2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>24000</v>
       </c>
       <c r="AI2">
         <f t="shared" si="0"/>
-        <v>8.25</v>
+        <v>24750</v>
       </c>
       <c r="AJ2">
-        <f>AI2+0.25</f>
-        <v>8.5</v>
+        <f t="shared" si="0"/>
+        <v>25500</v>
       </c>
       <c r="AK2">
-        <f t="shared" ref="AK2:AO2" si="1">AJ2+0.25</f>
-        <v>8.75</v>
+        <f t="shared" si="0"/>
+        <v>26250</v>
       </c>
       <c r="AL2">
+        <f t="shared" si="0"/>
+        <v>27000</v>
+      </c>
+      <c r="AM2">
+        <f t="shared" si="0"/>
+        <v>27750</v>
+      </c>
+      <c r="AN2">
+        <f t="shared" si="0"/>
+        <v>28500</v>
+      </c>
+      <c r="AO2">
+        <f t="shared" si="0"/>
+        <v>29250</v>
+      </c>
+      <c r="AP2">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="AQ2">
+        <f t="shared" si="0"/>
+        <v>30750</v>
+      </c>
+      <c r="AR2">
+        <f t="shared" si="0"/>
+        <v>31500</v>
+      </c>
+      <c r="AS2">
+        <f t="shared" si="0"/>
+        <v>32250</v>
+      </c>
+      <c r="AT2">
+        <f t="shared" si="0"/>
+        <v>33000</v>
+      </c>
+      <c r="AU2">
+        <f t="shared" si="0"/>
+        <v>33750</v>
+      </c>
+      <c r="AV2">
+        <f t="shared" si="0"/>
+        <v>34500</v>
+      </c>
+      <c r="AW2">
+        <f t="shared" si="0"/>
+        <v>35250</v>
+      </c>
+      <c r="AX2">
+        <f t="shared" si="0"/>
+        <v>36000</v>
+      </c>
+      <c r="AY2">
+        <f t="shared" si="0"/>
+        <v>36750</v>
+      </c>
+      <c r="AZ2">
+        <f t="shared" si="0"/>
+        <v>37500</v>
+      </c>
+      <c r="BA2">
+        <f t="shared" si="0"/>
+        <v>38250</v>
+      </c>
+      <c r="BB2">
+        <f t="shared" si="0"/>
+        <v>39000</v>
+      </c>
+      <c r="BC2">
+        <f t="shared" si="0"/>
+        <v>39750</v>
+      </c>
+      <c r="BD2">
+        <f t="shared" si="0"/>
+        <v>40500</v>
+      </c>
+      <c r="BE2">
+        <f t="shared" si="0"/>
+        <v>41250</v>
+      </c>
+      <c r="BF2">
+        <f t="shared" si="0"/>
+        <v>42000</v>
+      </c>
+      <c r="BG2">
+        <f t="shared" si="0"/>
+        <v>42750</v>
+      </c>
+      <c r="BH2">
+        <f t="shared" si="0"/>
+        <v>43500</v>
+      </c>
+      <c r="BI2">
+        <f t="shared" si="0"/>
+        <v>44250</v>
+      </c>
+      <c r="BJ2">
+        <f t="shared" si="0"/>
+        <v>45000</v>
+      </c>
+      <c r="BK2">
+        <f t="shared" si="0"/>
+        <v>45750</v>
+      </c>
+      <c r="BL2">
+        <f t="shared" si="0"/>
+        <v>46500</v>
+      </c>
+      <c r="BM2">
+        <f t="shared" si="0"/>
+        <v>47250</v>
+      </c>
+      <c r="BN2">
+        <f t="shared" si="0"/>
+        <v>48000</v>
+      </c>
+      <c r="BO2">
+        <f t="shared" si="0"/>
+        <v>48750</v>
+      </c>
+      <c r="BP2">
+        <f t="shared" ref="BP2:CE2" si="1">BO2+750</f>
+        <v>49500</v>
+      </c>
+      <c r="BQ2">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="AM2">
+        <v>50250</v>
+      </c>
+      <c r="BR2">
         <f t="shared" si="1"/>
-        <v>9.25</v>
-      </c>
-      <c r="AN2">
+        <v>51000</v>
+      </c>
+      <c r="BS2">
         <f t="shared" si="1"/>
-        <v>9.5</v>
-      </c>
-      <c r="AO2">
+        <v>51750</v>
+      </c>
+      <c r="BT2">
         <f t="shared" si="1"/>
-        <v>9.75</v>
-      </c>
-      <c r="AP2">
-        <f>AO2+0.25</f>
-        <v>10</v>
-      </c>
-      <c r="AQ2">
-        <f t="shared" ref="AQ2:BJ2" si="2">AP2+0.25</f>
-        <v>10.25</v>
-      </c>
-      <c r="AR2">
-        <f t="shared" si="2"/>
-        <v>10.5</v>
-      </c>
-      <c r="AS2">
-        <f t="shared" si="2"/>
-        <v>10.75</v>
-      </c>
-      <c r="AT2">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="AU2">
-        <f t="shared" si="2"/>
-        <v>11.25</v>
-      </c>
-      <c r="AV2">
-        <f t="shared" si="2"/>
-        <v>11.5</v>
-      </c>
-      <c r="AW2">
-        <f t="shared" si="2"/>
-        <v>11.75</v>
-      </c>
-      <c r="AX2">
-        <f t="shared" si="2"/>
-        <v>12</v>
-      </c>
-      <c r="AY2">
-        <f t="shared" si="2"/>
-        <v>12.25</v>
-      </c>
-      <c r="AZ2">
-        <f t="shared" si="2"/>
-        <v>12.5</v>
-      </c>
-      <c r="BA2">
-        <f t="shared" si="2"/>
-        <v>12.75</v>
-      </c>
-      <c r="BB2">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="BC2">
-        <f t="shared" si="2"/>
-        <v>13.25</v>
-      </c>
-      <c r="BD2">
-        <f t="shared" si="2"/>
-        <v>13.5</v>
-      </c>
-      <c r="BE2">
-        <f t="shared" si="2"/>
-        <v>13.75</v>
-      </c>
-      <c r="BF2">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="BG2">
-        <f t="shared" si="2"/>
-        <v>14.25</v>
-      </c>
-      <c r="BH2">
-        <f t="shared" si="2"/>
-        <v>14.5</v>
-      </c>
-      <c r="BI2">
-        <f t="shared" si="2"/>
-        <v>14.75</v>
-      </c>
-      <c r="BJ2">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="BK2">
-        <f t="shared" ref="BK2" si="3">BJ2+0.25</f>
-        <v>15.25</v>
-      </c>
-      <c r="BL2">
-        <f t="shared" ref="BL2" si="4">BK2+0.25</f>
-        <v>15.5</v>
-      </c>
-      <c r="BM2">
-        <f t="shared" ref="BM2" si="5">BL2+0.25</f>
-        <v>15.75</v>
-      </c>
-      <c r="BN2">
-        <f t="shared" ref="BN2" si="6">BM2+0.25</f>
-        <v>16</v>
-      </c>
-      <c r="BO2">
-        <f t="shared" ref="BO2" si="7">BN2+0.25</f>
-        <v>16.25</v>
-      </c>
-      <c r="BP2">
-        <f t="shared" ref="BP2" si="8">BO2+0.25</f>
-        <v>16.5</v>
-      </c>
-      <c r="BQ2">
-        <f t="shared" ref="BQ2" si="9">BP2+0.25</f>
-        <v>16.75</v>
-      </c>
-      <c r="BR2">
-        <f t="shared" ref="BR2" si="10">BQ2+0.25</f>
-        <v>17</v>
-      </c>
-      <c r="BS2">
-        <f t="shared" ref="BS2" si="11">BR2+0.25</f>
-        <v>17.25</v>
-      </c>
-      <c r="BT2">
-        <f t="shared" ref="BT2" si="12">BS2+0.25</f>
-        <v>17.5</v>
+        <v>52500</v>
       </c>
       <c r="BU2">
-        <f t="shared" ref="BU2" si="13">BT2+0.25</f>
-        <v>17.75</v>
+        <f t="shared" si="1"/>
+        <v>53250</v>
       </c>
       <c r="BV2">
-        <f t="shared" ref="BV2" si="14">BU2+0.25</f>
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>54000</v>
       </c>
       <c r="BW2">
-        <f t="shared" ref="BW2" si="15">BV2+0.25</f>
-        <v>18.25</v>
+        <f t="shared" si="1"/>
+        <v>54750</v>
       </c>
       <c r="BX2">
-        <f t="shared" ref="BX2" si="16">BW2+0.25</f>
-        <v>18.5</v>
+        <f t="shared" si="1"/>
+        <v>55500</v>
       </c>
       <c r="BY2">
-        <f t="shared" ref="BY2" si="17">BX2+0.25</f>
-        <v>18.75</v>
+        <f t="shared" si="1"/>
+        <v>56250</v>
       </c>
       <c r="BZ2">
-        <f t="shared" ref="BZ2" si="18">BY2+0.25</f>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>57000</v>
       </c>
       <c r="CA2">
-        <f t="shared" ref="CA2" si="19">BZ2+0.25</f>
-        <v>19.25</v>
+        <f t="shared" si="1"/>
+        <v>57750</v>
       </c>
       <c r="CB2">
-        <f t="shared" ref="CB2" si="20">CA2+0.25</f>
-        <v>19.5</v>
+        <f t="shared" si="1"/>
+        <v>58500</v>
       </c>
       <c r="CC2">
-        <f t="shared" ref="CC2" si="21">CB2+0.25</f>
-        <v>19.75</v>
+        <f t="shared" si="1"/>
+        <v>59250</v>
       </c>
       <c r="CD2">
-        <f t="shared" ref="CD2" si="22">CC2+0.25</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>60000</v>
       </c>
       <c r="CE2">
-        <v>1000</v>
-      </c>
-      <c r="CF2">
-        <v>10000</v>
+        <f t="shared" si="1"/>
+        <v>60750</v>
+      </c>
+      <c r="CF2" s="2">
+        <v>1000000</v>
       </c>
     </row>
   </sheetData>
@@ -6095,17 +6095,17 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -6124,12 +6124,12 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -6699,102 +6699,102 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="D7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="E7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="H7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="J7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="K7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="M7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="N7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="O7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="P7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="Q7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="R7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="S7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="T7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="U7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="V7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="W7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="X7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="Y7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="Z7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AA7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AB7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AC7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AD7">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AE7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -6889,7 +6889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -6984,7 +6984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -7459,7 +7459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -7554,7 +7554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -7649,7 +7649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -7839,7 +7839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -8314,7 +8314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -8409,7 +8409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>
